--- a/naver-place-crawler/results_nail/송도_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/송도_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>모드니네일 송도점</t>
+          <t>송도네일송도속눈썹 모요네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dkaktsk03@naver.com</t>
+          <t>wldms9369@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1318-7860</t>
+          <t>0507-1317-5733</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
+          <t>인천광역시 연수구 센트럴로 313 A동 218호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dkaktsk03</t>
+          <t>http://pf.kakao.com/_GyhrG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,22 +601,18 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49p11</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1313369427</t>
+          <t>1202013138</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1313369427</t>
+          <t>https://m.place.naver.com/place/1202013138</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일뮬</t>
+          <t>몰튼네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jhoe4568@naver.com</t>
+          <t>ivygreentee@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1474-2412</t>
+          <t>0507-1413-7890</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
+          <t>인천광역시 연수구 센트럴로 160 판매시설동 1층 148호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/molten_nailmood?igsh=MW9ob3V5dnYzM3F1aQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>239</v>
+        <v>348</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="R3" t="n">
-        <v>301</v>
+        <v>379</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1415557011</t>
+          <t>36307393</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1415557011</t>
+          <t>https://m.place.naver.com/place/36307393</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이로울뷰티</t>
+          <t>폼</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iroulbeauty@naver.com</t>
+          <t>marketerzip@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1420-8565</t>
+          <t>032-446-2222</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
+          <t>인천광역시 연수구 랜드마크로 160 마리나베이 후문 미송초 건너편 1층 상가</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iiroul.nail</t>
+          <t>https://www.instagram.com/porm_songdo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>827</v>
+        <v>309</v>
       </c>
       <c r="Q4" t="n">
-        <v>515</v>
+        <v>31</v>
       </c>
       <c r="R4" t="n">
-        <v>1342</v>
+        <v>340</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1745367791</t>
+          <t>1272387955</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745367791</t>
+          <t>https://m.place.naver.com/place/1272387955</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피치스네일 송도점</t>
+          <t>볼네일 인천송도점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>peaches_nail@naver.com</t>
+          <t>ballnail-@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1363-8301</t>
+          <t>0507-1341-0638</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 A동 1층 129-1호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://peachesnail.co.kr/</t>
+          <t>https://www.instagram.com/ballnail_</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -898,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="Q5" t="n">
-        <v>956</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>1354</v>
+        <v>402</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1241378115</t>
+          <t>2002201349</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241378115</t>
+          <t>https://m.place.naver.com/place/2002201349</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -944,34 +940,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오뉴월뷰티</t>
+          <t>오벨리뷰티 레푸스 송도점&amp;내성발톱 문제성발 발각질</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vanilla__-@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>ehdgml320@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>refuss02@tatek.co.kr</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1338-4181</t>
+          <t>0507-1355-7923</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
+          <t>인천광역시 연수구 하모니로138번길 11 캐슬센트럴파크 101동 212호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/onewwol_bty</t>
+          <t>http://www.refuss.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>688</v>
+        <v>78</v>
       </c>
       <c r="Q6" t="n">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="R6" t="n">
-        <v>855</v>
+        <v>137</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1572480675</t>
+          <t>1748372244</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572480675</t>
+          <t>https://m.place.naver.com/place/1748372244</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
+          <t>러브빈네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bal-eul@naver.com</t>
+          <t>dpflswlsgur7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1397-2100</t>
+          <t>0507-1402-0544</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
+          <t>인천광역시 연수구 랜드마크로 20 송도호반써밋 상가 2층 233호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bal-eul</t>
+          <t>https://www.instagram.com/luvvin_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Q7" t="n">
-        <v>423</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>541</v>
+        <v>126</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1837101349</t>
+          <t>1023244566</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837101349</t>
+          <t>https://m.place.naver.com/place/1023244566</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1132,25 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일1607</t>
+          <t>네일바이뚜</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tammi1607@naver.com</t>
+          <t>byl1003@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1340-2987</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 상가 2층 221</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail160_7</t>
+          <t>https://www.instagram.com/nail_by_ddu</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,17 +1174,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42huz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>442</v>
+        <v>217</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="R8" t="n">
-        <v>473</v>
+        <v>269</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1249527516</t>
+          <t>1515520159</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249527516</t>
+          <t>https://m.place.naver.com/place/1515520159</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>차차뷰티네일</t>
+          <t>네일르블랑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yjk9092@naver.com</t>
+          <t>6540067@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1345-2926</t>
+          <t>0507-1306-8906</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 센트럴로 313 B동 239호</t>
+          <t>인천광역시 연수구 인천타워대로 393 305동 1층 A동 112호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/chachabt_1</t>
+          <t>https://www.instagram.com/nail_le_blanc</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4u3vm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1287,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>276</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>354</v>
+        <v>13</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1945183541</t>
+          <t>2085102425</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945183541</t>
+          <t>https://m.place.naver.com/place/2085102425</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>반디인하우스 송도점</t>
+          <t>힐링네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bandinhouse_songdo@naver.com</t>
+          <t>lovekeiti@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1434-8241</t>
+          <t>0507-1330-2935</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
+          <t>인천광역시 연수구 해돋이로 107 G동 1층 상가56호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bandinhouse_songdo</t>
+          <t>https://www.instagram.com/healing08_nail/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1361,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1372,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>269</v>
+        <v>58</v>
       </c>
       <c r="Q10" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1592116315</t>
+          <t>35051773</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1592116315</t>
+          <t>https://m.place.naver.com/place/35051773</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
+          <t>스튜디오에텡</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bonyi-@naver.com</t>
+          <t>studio_etein@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1317-7310</t>
+          <t>0507-1335-0210</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
+          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/podlab_songdo/</t>
+          <t>https://blog.naver.com/studio_etein/224234215441</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1466,7 +1462,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>651</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>389</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1040</v>
+        <v>16</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1486,6099 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>2046081988</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046081988</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>네일 그리다</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nailgrida_@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1310-1421</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 107 퍼스트월드 H동 1층 25-1호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_XRMxjT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>34</v>
+      </c>
+      <c r="R12" t="n">
+        <v>133</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1953707821</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1953707821</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>러브윤네일</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>kyj_lovely@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>032-815-3399</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도국제대로 261 더샵 센트럴시티 217동 상가 1층 118호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luvyun_nail?igsh=MTB5dnRza3I1czVydA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>40</v>
+      </c>
+      <c r="R13" t="n">
+        <v>231</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1231000131</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1231000131</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>누오네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>moekgomasigo@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1481-2504</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 165-17 2층 231호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_rJBWG</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
+        <v>140</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1196589400</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196589400</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>모드니네일 송도점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dkaktsk03@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1318-7860</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dkaktsk03</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16</v>
+      </c>
+      <c r="R15" t="n">
+        <v>385</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1313369427</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1313369427</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>미니네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wjdalsdl1204@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1341-6562</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 2층 207호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/wjdalsdl1204</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10</v>
+      </c>
+      <c r="R16" t="n">
+        <v>254</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1932500802</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932500802</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>네일이다</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>edukin_edu@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1369-0577</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로 56 송도BT센터 206호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xjxcxlxhb</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>27</v>
+      </c>
+      <c r="R17" t="n">
+        <v>66</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1452205227</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1452205227</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>비네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>bi__nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 27 203동 C221</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bi__nail</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>22</v>
+      </c>
+      <c r="R18" t="n">
+        <v>103</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2030460161</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030460161</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>아랑네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>arang827@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설상가 213호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/arang_nail_/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>287</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1956613046</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1956613046</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bonyi-@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1317-7310</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/podlab_songdo/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>392</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1044</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>1701093046</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1701093046</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>네일라벨르 송도타임스페이스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>join9360@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1362-9360</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 314호 네일라벨르</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/join9360</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1287</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>14</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1301</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1280755213</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280755213</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>네일이루나 타임스페이스</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dbdlzkzn123@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 C동 307호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_txdhKG</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>478</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>22</v>
+      </c>
+      <c r="R22" t="n">
+        <v>500</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1227897061</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1227897061</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pausa nail artment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>loveruru_@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1465-3039</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 257 송도아트포레 1층 137호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pausa_nail.artment?igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>118</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1410434423</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1410434423</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>데이지네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>a1070bbb@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1444-9334</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 144 A동 2층 213호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sKSaW3Sg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>155</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1462227411</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462227411</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ckdwnrewq@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1321-6532</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로125번길 13 아크리아1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ckdwnrewq</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>201</v>
+      </c>
+      <c r="R25" t="n">
+        <v>776</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>21216458</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21216458</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>발라발라네일 송도점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ballaballa0-7-0-2@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1408-9365</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 A동 133호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>296</v>
+      </c>
+      <c r="R26" t="n">
+        <v>571</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>933071487</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/933071487</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>피어라뷰티샵</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ppghddid_@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1343-1828</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크101동201호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xcxelwK</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>754</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>226</v>
+      </c>
+      <c r="R27" t="n">
+        <v>980</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>36957559</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36957559</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>김소형네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hcl9207@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1374-3322</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 161 세종프라자 103호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B0qqrMQg9L1/?igshid=i4dcis0v7xyx</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>129</v>
+      </c>
+      <c r="R28" t="n">
+        <v>447</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1850651021</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850651021</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>뤼미에트네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hbs2002i@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1347-2495</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 210호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhgxgxon</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>52</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2019651969</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019651969</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>네일모아나</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7daystaste@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1403-1161</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 232 GATE , E1 1층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailmoana_</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>143</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1865551764</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1865551764</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>네일뮤 네일&amp;패디</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sharue_88@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1449-0613</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nail._.meow</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1488</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>110</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1598</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1446087577</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446087577</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>비지트네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>visitnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1394-9422</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 C동 341호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/visitnail</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>47</v>
+      </c>
+      <c r="R32" t="n">
+        <v>133</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1503164148</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1503164148</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>하이피네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hy_p_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1365-6641</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 오피스텔동 107호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hy_p_nail</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>71</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1213017361</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213017361</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>발라발라네일스파 국제업무지구역점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ballaballa0-7-0-2@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1388-1058</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크B동334호 발라발라네일스파</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>273</v>
+      </c>
+      <c r="R34" t="n">
+        <v>412</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1290046405</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1290046405</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>순수네일 송도</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>rlarkgo1991@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1334-1809</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 B동 125호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlarkgo1991</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>359</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>84</v>
+      </c>
+      <c r="R35" t="n">
+        <v>443</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1265228777</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1265228777</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>운디아르</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ultimateworldtravel@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1388-8519</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A124</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/undiar_nail_atelier/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>127</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2073953295</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2073953295</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아티카네일 송도</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>atticanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1355-9531</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크 C동 2층 258호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/atticanail</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>119</v>
+      </c>
+      <c r="R37" t="n">
+        <v>341</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1192730169</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192730169</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>모모네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>yangereek92@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1449-3429</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로274번길 55 상가동 1층 6호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__momo.nail</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>169</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1312635729</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312635729</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>네일민</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cej909@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 116 푸르지오월드마크7단지 1층 125호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Nail_Minae</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>45</v>
+      </c>
+      <c r="R39" t="n">
+        <v>344</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1769913626</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1769913626</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>다됨네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>a7814341@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>032-815-9344</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도문화로28번길 27 호반베르디움 2차 아파트상가 2동 204호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/a7814341</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>16</v>
+      </c>
+      <c r="R40" t="n">
+        <v>145</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1320993039</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320993039</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>네일잇</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>nail__it_@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1401-9180</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동314호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail__it_</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>128</v>
+      </c>
+      <c r="R41" t="n">
+        <v>668</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>878464897</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/878464897</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>반디인하우스 송도점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bandinhouse_songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1434-8241</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bandinhouse_songdo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>72</v>
+      </c>
+      <c r="R42" t="n">
+        <v>342</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1592116315</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1592116315</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>지금할일은네일로 송도점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>inquire_89296@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1322-1498</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 1층 193호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hong_nailshop</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>34</v>
+      </c>
+      <c r="R43" t="n">
+        <v>253</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1834821209</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1834821209</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>네일도맑음</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dusgml-91@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1370-8213</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 1층 166호 리치센트럴</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naildo_malkum</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>22</v>
+      </c>
+      <c r="R44" t="n">
+        <v>458</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1724575080</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1724575080</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>이로울뷰티</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>iroulbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1420-8565</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iiroul.nail</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>837</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>519</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1356</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1745367791</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1745367791</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>오빛나네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jjw_1117@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 A동 3층 317호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/obitna_nail</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>623</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>151</v>
+      </c>
+      <c r="R46" t="n">
+        <v>774</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1076777712</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1076777712</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>네일뮬</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>catrabbit18@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1474-2412</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>63</v>
+      </c>
+      <c r="R47" t="n">
+        <v>303</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1415557011</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1415557011</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>네일에르</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>bo_reum22@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1412-8155</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 2층 211호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail___aile/?next=undefined&amp;hl=ko</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>10</v>
+      </c>
+      <c r="R48" t="n">
+        <v>90</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2024964834</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024964834</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>앤드네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>alsgkwjd12@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1478-8939</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 랜드마크로 20 판매시설 2층 230호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_andnail</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>333</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1327958684</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1327958684</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>네일1607</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>tammi1607@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail160_7</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>445</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>31</v>
+      </c>
+      <c r="R50" t="n">
+        <v>476</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1249527516</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1249527516</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>그린닷네일 뷰티</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>palette_j_1107@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1351-8538</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grin.dot_nail/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>16</v>
+      </c>
+      <c r="R51" t="n">
+        <v>194</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1912589928</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1912589928</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일 109 송도점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nail_109@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1319-1218</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 131 여름동 149호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_109</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>67</v>
+      </c>
+      <c r="R52" t="n">
+        <v>476</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1414664528</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1414664528</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>문제성발관리센터 메디푸스 내성발톱 무좀 각질 문제성발톱</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>medifuss@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1321-3367</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 131 201동 213호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/medifuss</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>165</v>
+      </c>
+      <c r="R53" t="n">
+        <v>427</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1696402748</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1696402748</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>연주뷰티</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ods06060@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1495-0793</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로6번길 7 성지리벨루스 상가 2층 201호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeon_ju_bty?igsh=MXJldDdweXgxNml2dA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>71</v>
+      </c>
+      <c r="R54" t="n">
+        <v>418</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1902277385</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1902277385</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>무이트네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gonazzing@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1301-1100</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 A동 128호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muit_nail</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>11</v>
+      </c>
+      <c r="R55" t="n">
+        <v>80</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2019520350</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019520350</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>유데이네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>siripark85@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1460-2465</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설동 132호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yud_nail7/</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>89</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2042349151</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2042349151</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>후쓰네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>white5198@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1436-7955</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 107 더샵 퍼스트월드 H동 11호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_WinDT</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>22</v>
+      </c>
+      <c r="R57" t="n">
+        <v>252</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>798831444</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/798831444</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>bal-eul@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1397-2100</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bal-eul</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>422</v>
+      </c>
+      <c r="R58" t="n">
+        <v>540</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1837101349</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1837101349</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>모찌네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>denise1003@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 C동 4층 410호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mochinail_eb</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>17</v>
+      </c>
+      <c r="R59" t="n">
+        <v>169</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1205962180</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205962180</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>피치스네일 송도점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>peaches_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1363-8301</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://peachesnail.co.kr/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>701</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1102</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1241378115</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241378115</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>송도네일무아</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>babbab123-@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1305-5796</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드,G동 상가 1층 43호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_mua_songdo?igsh=MWt6d3U1bjk1NzQweg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>10</v>
+      </c>
+      <c r="R61" t="n">
+        <v>162</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2036597442</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036597442</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일포유</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nail_for_u@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1374-7708</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 122 107호 네일포유</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailforyou_/</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>8</v>
+      </c>
+      <c r="R62" t="n">
+        <v>56</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>36177492</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36177492</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>블링앤네일 송도점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bling_n_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1362-1590</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 144 지웰 푸르지오시티 상가 A동 203호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/bling_n_nail</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>69</v>
+      </c>
+      <c r="R63" t="n">
+        <v>371</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1993531345</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1993531345</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>스무살롱네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1465-7994</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 랜드마크로 68 301동 250호 스무살롱네일</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/20salon_nail?igsh=eGE3NXdzeDgzaDl5&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>20</v>
+      </c>
+      <c r="R64" t="n">
+        <v>111</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1287550429</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1287550429</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>딜라잇네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dedicatedperson@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1388-1456</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 194 센트럴파크2 상가C동 1층 113호 c2게이트</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_iepFT</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>29</v>
+      </c>
+      <c r="R65" t="n">
+        <v>57</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>954314232</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/954314232</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>차차뷰티네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>yjk9092@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1345-2926</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 B동 239호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://instagram.com/chachabt_1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>78</v>
+      </c>
+      <c r="R66" t="n">
+        <v>354</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1945183541</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945183541</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>나다운네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>xau123@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1376-9480</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 3층 315호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_YRZMs</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4</v>
+      </c>
+      <c r="R67" t="n">
+        <v>12</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1120623548</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120623548</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일은예쁘게</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>beautifulnail_day@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1324-0261</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 50 푸르지오월드마크1단지 118호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/beautifulnail_day</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>10</v>
+      </c>
+      <c r="R68" t="n">
+        <v>62</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1923525963</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1923525963</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네일이끌림</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>luxury24@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1464-4142</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티오피스텔상가204동2층220호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_2ggellim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>577</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>99</v>
+      </c>
+      <c r="R69" t="n">
+        <v>676</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1369252408</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1369252408</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일르헤브</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>todaysarangtoday@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1363-9064</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 116 145호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_le_reve</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>6</v>
+      </c>
+      <c r="R70" t="n">
+        <v>120</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1359293825</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359293825</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일포레</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nail_foret@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1335-3598</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 257 아트포레 C동 102호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_foret</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>215</v>
+      </c>
+      <c r="R71" t="n">
+        <v>413</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1709958460</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1709958460</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>하꼼네일 파고드는발톱 문제성발톱 발각질</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>maesa01@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1364-7451</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 A동 2층 208호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wvvmG</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>5</v>
+      </c>
+      <c r="R72" t="n">
+        <v>277</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1024262947</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1024262947</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>언니솜씨 송도점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jornardan@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>032-832-4177</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로97번길 30 근린상가 106호 언니솜씨</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sister__nail__</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>137</v>
+      </c>
+      <c r="R73" t="n">
+        <v>396</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1559564560</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1559564560</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>오뉴월뷰티</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>vanilla__-@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1338-4181</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/onewwol_bty</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>696</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>172</v>
+      </c>
+      <c r="R74" t="n">
+        <v>868</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1572480675</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1572480675</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>더 예뻐질 네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>nail4season@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>032-851-1488</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로132번길 9 C동 236호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/__pretty_nail</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>45</v>
+      </c>
+      <c r="R75" t="n">
+        <v>366</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1495079740</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1495079740</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>인어뷰티 송도점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>in_awe_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1397-2403</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in.awe.beauty</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>665</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>130</v>
+      </c>
+      <c r="R76" t="n">
+        <v>795</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1323913451</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1323913451</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/송도_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/송도_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>이로울뷰티</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>iroulbeauty@naver.com</t>
-        </is>
-      </c>
+          <t>폼</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1420-8565</t>
+          <t>032-446-2222</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
+          <t>인천광역시 연수구 랜드마크로 160 마리나베이 후문 미송초 건너편 1층 상가</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iiroul.nail</t>
+          <t>https://www.instagram.com/porm_songdo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>848</v>
+        <v>312</v>
       </c>
       <c r="Q2" t="n">
-        <v>522</v>
+        <v>31</v>
       </c>
       <c r="R2" t="n">
-        <v>1370</v>
+        <v>343</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1745367791</t>
+          <t>1272387955</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745367791</t>
+          <t>https://m.place.naver.com/place/1272387955</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +654,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>bal-eul@naver.com</t>
-        </is>
-      </c>
+          <t>앤드네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1397-2100</t>
+          <t>0507-1478-8939</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
+          <t>인천광역시 연수구 랜드마크로 20 판매시설 2층 230호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bal-eul</t>
+          <t>https://www.instagram.com/_andnail</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +687,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>118</v>
+        <v>328</v>
       </c>
       <c r="Q3" t="n">
-        <v>424</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>542</v>
+        <v>333</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +722,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1837101349</t>
+          <t>1327958684</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837101349</t>
+          <t>https://m.place.naver.com/place/1327958684</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +744,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>그린닷네일 뷰티</t>
+          <t>송도네일무아</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>palette_j_1107@naver.com</t>
+          <t>babbab123-@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1351-8538</t>
+          <t>0507-1305-5796</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
+          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드,G동 상가 1층 43호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grin.dot_nail/</t>
+          <t>https://www.instagram.com/nail_mua_songdo?igsh=MWt6d3U1bjk1NzQweg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +816,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1912589928</t>
+          <t>2036597442</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912589928</t>
+          <t>https://m.place.naver.com/place/2036597442</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +838,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일뮬</t>
+          <t>네일 그리다</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jhoe4568@naver.com</t>
+          <t>nailgrida_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1474-2412</t>
+          <t>0507-1310-1421</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
+          <t>인천광역시 연수구 해돋이로 107 퍼스트월드 H동 1층 25-1호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_XRMxjT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +886,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="R5" t="n">
-        <v>305</v>
+        <v>133</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1415557011</t>
+          <t>1953707821</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1415557011</t>
+          <t>https://m.place.naver.com/place/1953707821</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,25 +932,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일1607</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>darara5670@naver.com</t>
-        </is>
-      </c>
+          <t>이소뉴네일</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1362-4124</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
+          <t>인천광역시 연수구 컨벤시아대로42번길 25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail160_7</t>
+          <t>https://www.instagram.com/aesonue_nail/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +976,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>446</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>477</v>
+        <v>25</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1000,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1249527516</t>
+          <t>1542979841</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249527516</t>
+          <t>https://m.place.naver.com/place/1542979841</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,34 +1022,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>송도네일송도속눈썹 모요네일</t>
+          <t>다됨네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wldms9369@naver.com</t>
+          <t>a7814341@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1317-5733</t>
+          <t>032-815-9344</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 연수구 센트럴로 313 A동 218호</t>
+          <t>인천광역시 연수구 송도문화로28번길 27 호반베르디움 2차 아파트상가 2동 204호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GyhrG</t>
+          <t>https://blog.naver.com/a7814341</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1067,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1078,7 +1070,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>383</v>
+        <v>129</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R7" t="n">
-        <v>387</v>
+        <v>145</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1094,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1202013138</t>
+          <t>1320993039</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202013138</t>
+          <t>https://m.place.naver.com/place/1320993039</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1116,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일뮤 네일&amp;패디</t>
+          <t>네일라벨르 송도타임스페이스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sharue_88@naver.com</t>
+          <t>join9360@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1449-0613</t>
+          <t>0507-1362-9360</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 314호 네일라벨르</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://instagram.com/nail._.meow</t>
+          <t>https://blog.naver.com/join9360</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,22 +1153,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ch0z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1490</v>
+        <v>1288</v>
       </c>
       <c r="Q8" t="n">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1600</v>
+        <v>1302</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1188,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1446087577</t>
+          <t>1280755213</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446087577</t>
+          <t>https://m.place.naver.com/place/1280755213</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1210,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>인어뷰티 송도점</t>
+          <t>문제성발관리센터 메디푸스 내성발톱 무좀 각질 문제성발톱</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>in_awe_beauty@naver.com</t>
+          <t>medifuss@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1397-2403</t>
+          <t>0507-1321-3367</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
+          <t>인천광역시 연수구 아트센터대로 131 201동 213호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/in.awe.beauty</t>
+          <t>https://blog.naver.com/medifuss</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,19 +1247,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xurq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>666</v>
+        <v>264</v>
       </c>
       <c r="Q9" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="R9" t="n">
-        <v>796</v>
+        <v>429</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1323913451</t>
+          <t>1696402748</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323913451</t>
+          <t>https://m.place.naver.com/place/1696402748</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,34 +1304,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>차차뷰티네일</t>
+          <t>미니네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yjk9092@naver.com</t>
+          <t>wjdalsdl1204@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1345-2926</t>
+          <t>0507-1341-6562</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 센트럴로 313 B동 239호</t>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 2층 207호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://instagram.com/chachabt_1</t>
+          <t>https://link.inpock.co.kr/wjdalsdl1204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1357,19 +1341,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4u3vm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,17 +1357,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="Q10" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>354</v>
+        <v>256</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1376,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1945183541</t>
+          <t>1932500802</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945183541</t>
+          <t>https://m.place.naver.com/place/1932500802</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,29 +1398,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일르블랑</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6540067@naver.com</t>
-        </is>
-      </c>
+          <t>지금할일은네일로 송도점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1306-8906</t>
+          <t>0507-1322-1498</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 인천타워대로 393 305동 1층 A동 112호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 1층 193호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le_blanc</t>
+          <t>https://www.instagram.com/hong_nailshop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1460,14 +1436,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wtk6cqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1479,13 +1451,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>253</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1466,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2085102425</t>
+          <t>1834821209</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085102425</t>
+          <t>https://m.place.naver.com/place/1834821209</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1516,29 +1488,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스튜디오에텡</t>
+          <t>네일 109 송도점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>studio_etein@naver.com</t>
+          <t>nail_109@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1335-0210</t>
+          <t>0507-1319-1218</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
+          <t>인천광역시 연수구 아트센터대로 131 여름동 149호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studio_etein/224234215441</t>
+          <t>https://blog.naver.com/nail_109</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1573,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>414</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="R12" t="n">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1588,12 +1560,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2046081988</t>
+          <t>1414664528</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046081988</t>
+          <t>https://m.place.naver.com/place/1414664528</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1610,29 +1582,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>트라움네일</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>la_mienne1401@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이뚜</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1312-2073</t>
+          <t>0507-1340-2987</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-14 306호</t>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 상가 2층 221</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/traum.nail_songdo?igsh=MTJsNHB2djA3ZDgyNQ==</t>
+          <t>https://www.instagram.com/nail_by_ddu</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1652,14 +1620,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4y8qbj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1671,30 +1635,5900 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>269</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1515520159</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1515520159</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>네일모아나</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1403-1161</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 232 GATE , E1 1층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailmoana_</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>143</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1865551764</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1865551764</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>유데이네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1460-2465</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설동 132호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yud_nail7/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>89</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2042349151</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2042349151</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차차뷰티네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1345-2926</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 B동 239호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://instagram.com/chachabt_1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>78</v>
+      </c>
+      <c r="R16" t="n">
+        <v>354</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1945183541</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945183541</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>누오네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1481-2504</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 165-17 2층 231호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_rJBWG</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>11</v>
+      </c>
+      <c r="R17" t="n">
+        <v>140</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1196589400</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196589400</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>네일에르</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1412-8155</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 2층 211호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail___aile/?next=undefined&amp;hl=ko</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" t="n">
+        <v>92</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2024964834</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024964834</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>무이트네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1301-1100</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 A동 128호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muit_nail</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>11</v>
+      </c>
+      <c r="R19" t="n">
+        <v>81</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2019520350</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019520350</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>로베네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1424-7675</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 365 C동 2층 207호 로베네일</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lovae_nail</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>116</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2044125264</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2044125264</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>bonyi-@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1317-7310</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/podlab_songdo/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>392</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1044</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1701093046</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1701093046</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>네일뮤 네일&amp;패디</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sharue_88@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1449-0613</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nail._.meow</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1490</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>110</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1446087577</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446087577</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>발라발라네일 송도점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ballaballa0-7-0-2@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1408-9365</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 A동 133호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>296</v>
+      </c>
+      <c r="R23" t="n">
+        <v>571</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>933071487</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/933071487</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>네일퀸 송도점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>seulbi8607@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1364-8343</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도국제대로 165 2층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PgXfn</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>56</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1969782774</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1969782774</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>하꼼네일 파고드는발톱 문제성발톱 발각질</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>maesa01@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1364-7451</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 A동 2층 208호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wvvmG</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>275</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1024262947</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1024262947</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>러브윤네일</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>kyj_lovely@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>032-815-3399</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도국제대로 261 더샵 센트럴시티 217동 상가 1층 118호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luvyun_nail?igsh=MTB5dnRza3I1czVydA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>40</v>
+      </c>
+      <c r="R26" t="n">
+        <v>231</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1231000131</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1231000131</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>연주뷰티</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ods06060@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1495-0793</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로6번길 7 성지리벨루스 상가 2층 201호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeon_ju_bty?igsh=MXJldDdweXgxNml2dA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>71</v>
+      </c>
+      <c r="R27" t="n">
+        <v>420</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1902277385</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1902277385</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>피치스네일 송도점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>peaches_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1363-8301</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://peachesnail.co.kr/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>402</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>701</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1103</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1241378115</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241378115</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>스튜디오에텡</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>studio_etein@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1335-0210</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/studio_etein/224234215441</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>18</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2046081988</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046081988</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>몰튼네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ivygreentee@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1413-7890</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 160 판매시설동 1층 148호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/molten_nailmood?igsh=MW9ob3V5dnYzM3F1aQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>31</v>
+      </c>
+      <c r="R30" t="n">
+        <v>380</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>36307393</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36307393</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>언니솜씨 송도점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jornardan@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>032-832-4177</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로97번길 30 근린상가 106호 언니솜씨</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sister__nail__</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>137</v>
+      </c>
+      <c r="R31" t="n">
+        <v>396</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1559564560</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1559564560</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>러브빈네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dpflswlsgur7@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1402-0544</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 랜드마크로 20 송도호반써밋 상가 2층 233호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luvvin_nail</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>126</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1023244566</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1023244566</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>수블링네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>share_story_632@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1330-8567</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 C동 260호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/subling_songdo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R33" t="n">
+        <v>115</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1209855396</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1209855396</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>운디아르</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ultimateworldtravel@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1388-8519</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A124</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/undiar_nail_atelier/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>129</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2073953295</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2073953295</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>뤼미에트네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hbs2002i@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1347-2495</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 210호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhgxgxon</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q35" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2081684555</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2081684555</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="R35" t="n">
+        <v>52</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2019651969</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019651969</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>모찌네일</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>denise1003@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 C동 4층 410호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mochinail_eb</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>17</v>
+      </c>
+      <c r="R36" t="n">
+        <v>169</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1205962180</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205962180</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pausa nail artment</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cheoone_@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1465-3039</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 257 송도아트포레 1층 137호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pausa_nail.artment?igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>12</v>
+      </c>
+      <c r="R37" t="n">
+        <v>118</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1410434423</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1410434423</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>반디인하우스 송도점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bandinhouse_songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1434-8241</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bandinhouse_songdo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>72</v>
+      </c>
+      <c r="R38" t="n">
+        <v>342</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1592116315</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1592116315</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>네일도맑음</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dusgml-91@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1370-8213</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 1층 166호 리치센트럴</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naildo_malkum</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>22</v>
+      </c>
+      <c r="R39" t="n">
+        <v>462</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1724575080</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1724575080</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>네일르헤브</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>todaysarangtoday@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1363-9064</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 116 145호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_le_reve</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>121</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1359293825</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359293825</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>네일이루나 타임스페이스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>minyoung5959@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 C동 307호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_txdhKG</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>481</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23</v>
+      </c>
+      <c r="R41" t="n">
+        <v>504</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1227897061</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1227897061</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>네일포레</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>nail_foret@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1335-3598</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 257 아트포레 C동 102호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_foret</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>215</v>
+      </c>
+      <c r="R42" t="n">
+        <v>413</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1709958460</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1709958460</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>오벨리뷰티 레푸스 송도점&amp;내성발톱 문제성발 발각질</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ehdgml320@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>refuss02@tatek.co.kr</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1355-7923</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 캐슬센트럴파크 101동 212호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://www.refuss.co.kr/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>59</v>
+      </c>
+      <c r="R43" t="n">
+        <v>136</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1748372244</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1748372244</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>나다운네일</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>xau123@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1376-9480</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 3층 315호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_YRZMs</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>12</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1120623548</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120623548</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bal-eul@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1397-2100</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bal-eul</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>425</v>
+      </c>
+      <c r="R45" t="n">
+        <v>543</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1837101349</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1837101349</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>비네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bi__nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 27 203동 C221</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bi__nail</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>22</v>
+      </c>
+      <c r="R46" t="n">
+        <v>105</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2030460161</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030460161</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>발라발라네일스파 국제업무지구역점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ballaballa0-7-0-2@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1388-1058</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크B동334호 발라발라네일스파</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>273</v>
+      </c>
+      <c r="R47" t="n">
+        <v>413</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1290046405</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1290046405</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ckdwnrewq@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1321-6532</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로125번길 13 아크리아1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ckdwnrewq</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>201</v>
+      </c>
+      <c r="R48" t="n">
+        <v>776</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>21216458</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21216458</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>모드니네일 송도점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dkaktsk03@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1318-7860</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dkaktsk03</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>16</v>
+      </c>
+      <c r="R49" t="n">
+        <v>386</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1313369427</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1313369427</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>힐링네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lovekeiti@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1330-2935</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 107 G동 1층 상가56호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/healing08_nail/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10</v>
+      </c>
+      <c r="R50" t="n">
+        <v>69</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>35051773</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35051773</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>순수네일 송도</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rlarkgo1991@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1334-1809</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 B동 125호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlarkgo1991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>84</v>
+      </c>
+      <c r="R51" t="n">
+        <v>444</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1265228777</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1265228777</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>송도네일송도속눈썹 모요네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>wldms9369@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1317-5733</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 A동 218호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_GyhrG</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>387</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1202013138</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1202013138</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>인어뷰티 송도점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>in_awe_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1397-2403</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in.awe.beauty</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>666</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>130</v>
+      </c>
+      <c r="R53" t="n">
+        <v>796</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1323913451</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1323913451</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>네일뮬</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>catrabbit18@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1474-2412</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>63</v>
+      </c>
+      <c r="R54" t="n">
+        <v>305</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1415557011</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1415557011</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>김소형네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hcl9207@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1374-3322</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 161 세종프라자 103호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/B0qqrMQg9L1/?igshid=i4dcis0v7xyx</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>129</v>
+      </c>
+      <c r="R55" t="n">
+        <v>447</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1850651021</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850651021</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>그린닷네일 뷰티</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>palette_j_1107@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1351-8538</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grin.dot_nail/</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>16</v>
+      </c>
+      <c r="R56" t="n">
+        <v>195</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1912589928</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1912589928</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>아티카네일 송도</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>atticanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1355-9531</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크 C동 2층 258호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/atticanail</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>119</v>
+      </c>
+      <c r="R57" t="n">
+        <v>341</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1192730169</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192730169</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>모모네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>yangereek92@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1449-3429</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로274번길 55 상가동 1층 6호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__momo.nail</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>169</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1312635729</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312635729</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>네일포유</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nail_for_u@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1374-7708</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 122 107호 네일포유</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailforyou_/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>56</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>36177492</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36177492</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>오빛나네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jjw_1117@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 A동 3층 317호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/obitna_nail</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>623</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>167</v>
+      </c>
+      <c r="R60" t="n">
+        <v>790</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1076777712</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1076777712</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>네일1607</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>darara5670@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail160_7</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>446</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>31</v>
+      </c>
+      <c r="R61" t="n">
+        <v>477</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1249527516</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1249527516</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>송도네일에디크 센트럴점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>sym_ja@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 185 센트럴비즈한라 2층 213일부호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_psxeCn</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>14</v>
+      </c>
+      <c r="R62" t="n">
+        <v>129</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1035124007</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1035124007</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>네일은예쁘게</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>beautifulnail_day@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1324-0261</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 50 푸르지오월드마크1단지 118호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/beautifulnail_day</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>10</v>
+      </c>
+      <c r="R63" t="n">
+        <v>62</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1923525963</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1923525963</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>오뉴월뷰티</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>vanilla__-@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1338-4181</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/onewwol_bty</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>700</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>172</v>
+      </c>
+      <c r="R64" t="n">
+        <v>872</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1572480675</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1572480675</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>볼네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ballnail-@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1341-0638</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 A동 1층 129-1호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ballnail_</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>15</v>
+      </c>
+      <c r="R65" t="n">
+        <v>405</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2002201349</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002201349</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>네일이끌림</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>luxury24@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1464-4142</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티오피스텔상가204동2층220호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_2ggellim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>579</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>99</v>
+      </c>
+      <c r="R66" t="n">
+        <v>678</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1369252408</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1369252408</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>데이지네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>a1070bbb@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1444-9334</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 144 A동 2층 213호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sKSaW3Sg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>155</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1462227411</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462227411</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>피어라뷰티샵</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ppghddid_@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1343-1828</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크101동201호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xcxelwK</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>755</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>226</v>
+      </c>
+      <c r="R68" t="n">
+        <v>981</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>36957559</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36957559</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>이로울뷰티</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>iroulbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1420-8565</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iiroul.nail</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>848</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>523</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1371</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1745367791</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1745367791</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>더나은네일</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>merryyear09@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1485-4141</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 50 1단지 1층 114호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://qr.kakao.com/talk/7cbEXWNK0rWftgZp4g4Uaq8oJKc-</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>34</v>
+      </c>
+      <c r="R70" t="n">
+        <v>43</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>36643790</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36643790</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>후쓰네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>white5198@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1436-7955</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 107 더샵 퍼스트월드 H동 11호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_WinDT</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>22</v>
+      </c>
+      <c r="R71" t="n">
+        <v>252</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>798831444</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/798831444</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>네일르블랑</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>6540067@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1306-8906</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 393 305동 1층 A동 112호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_le_blanc</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>18</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2085102425</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2085102425</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>하이피네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>hy_p_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1365-6641</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 오피스텔동 107호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hy_p_nail</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>5</v>
+      </c>
+      <c r="R73" t="n">
+        <v>73</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1213017361</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213017361</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일잇</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>nail__it_@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1401-9180</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동314호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail__it_</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>128</v>
+      </c>
+      <c r="R74" t="n">
+        <v>668</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>878464897</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/878464897</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>네일민</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>cej909@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 116 푸르지오월드마크7단지 1층 125호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Nail_Minae</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>45</v>
+      </c>
+      <c r="R75" t="n">
+        <v>346</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1769913626</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1769913626</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>비지트네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>visitnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1394-9422</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 C동 341호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/visitnail</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>47</v>
+      </c>
+      <c r="R76" t="n">
+        <v>133</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1503164148</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1503164148</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_nail/송도_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/송도_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>폼</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>네일잇</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nail__it_@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>032-446-2222</t>
+          <t>0507-1401-9180</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 160 마리나베이 후문 미송초 건너편 1층 상가</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동314호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/porm_songdo</t>
+          <t>https://blog.naver.com/nail__it_</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>312</v>
+        <v>540</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="R2" t="n">
-        <v>343</v>
+        <v>668</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1272387955</t>
+          <t>878464897</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272387955</t>
+          <t>https://m.place.naver.com/place/878464897</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -654,30 +658,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>앤드네일</t>
+          <t>네일이루나 타임스페이스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1478-8939</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 판매시설 2층 230호</t>
+          <t>인천광역시 연수구 하모니로 158 C동 307호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_andnail</t>
+          <t>http://pf.kakao.com/_txdhKG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>328</v>
+        <v>481</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>333</v>
+        <v>504</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1327958684</t>
+          <t>1227897061</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327958684</t>
+          <t>https://m.place.naver.com/place/1227897061</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -744,29 +744,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>송도네일무아</t>
+          <t>네일뮬</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>babbab123-@naver.com</t>
+          <t>catrabbit18@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1305-5796</t>
+          <t>0507-1474-2412</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드,G동 상가 1층 43호</t>
+          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mua_songdo?igsh=MWt6d3U1bjk1NzQweg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>151</v>
+        <v>242</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="R4" t="n">
-        <v>161</v>
+        <v>305</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2036597442</t>
+          <t>1415557011</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036597442</t>
+          <t>https://m.place.naver.com/place/1415557011</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,34 +838,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일 그리다</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>nailgrida_@naver.com</t>
-        </is>
-      </c>
+          <t>네일에르</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1310-1421</t>
+          <t>0507-1412-8155</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 퍼스트월드 H동 1층 25-1호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 2층 211호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XRMxjT</t>
+          <t>https://www.instagram.com/nail___aile/?next=undefined&amp;hl=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -886,7 +882,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -895,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +906,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1953707821</t>
+          <t>2024964834</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953707821</t>
+          <t>https://m.place.naver.com/place/2024964834</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,25 +928,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이소뉴네일</t>
+          <t>연주뷰티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1362-4124</t>
+          <t>0507-1495-0793</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로42번길 25</t>
+          <t>인천광역시 연수구 신송로6번길 7 성지리벨루스 상가 2층 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aesonue_nail/</t>
+          <t>https://www.instagram.com/yeon_ju_bty?igsh=MXJldDdweXgxNml2dA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,13 +981,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>349</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,17 +996,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1542979841</t>
+          <t>1902277385</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1542979841</t>
+          <t>https://m.place.naver.com/place/1902277385</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1022,29 +1018,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>다됨네일</t>
+          <t>발라발라네일스파 국제업무지구역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>a7814341@naver.com</t>
+          <t>ballaballa0-7-0-2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-815-9344</t>
+          <t>0507-1388-1058</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도문화로28번길 27 호반베르디움 2차 아파트상가 2동 204호</t>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크B동334호 발라발라네일스파</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/a7814341</t>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,17 +1071,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="R7" t="n">
-        <v>145</v>
+        <v>413</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1320993039</t>
+          <t>1290046405</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320993039</t>
+          <t>https://m.place.naver.com/place/1290046405</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1116,34 +1112,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일라벨르 송도타임스페이스</t>
+          <t>미니네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>join9360@naver.com</t>
+          <t>wjdalsdl1204@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1362-9360</t>
+          <t>0507-1341-6562</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 314호 네일라벨르</t>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 2층 207호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/join9360</t>
+          <t>https://link.inpock.co.kr/wjdalsdl1204</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1164,22 +1160,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1288</v>
+        <v>246</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1302</v>
+        <v>256</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1280755213</t>
+          <t>1932500802</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280755213</t>
+          <t>https://m.place.naver.com/place/1932500802</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1210,34 +1206,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>문제성발관리센터 메디푸스 내성발톱 무좀 각질 문제성발톱</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>medifuss@naver.com</t>
-        </is>
-      </c>
+          <t>누오네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1321-3367</t>
+          <t>0507-1481-2504</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 131 201동 213호</t>
+          <t>인천광역시 연수구 신송로 165-17 2층 231호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/medifuss</t>
+          <t>http://pf.kakao.com/_rJBWG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1247,7 +1239,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1258,7 +1250,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1267,13 +1259,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="Q9" t="n">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>429</v>
+        <v>140</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,17 +1274,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1696402748</t>
+          <t>1196589400</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696402748</t>
+          <t>https://m.place.naver.com/place/1196589400</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1304,29 +1296,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>미니네일</t>
+          <t>피어라뷰티샵</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wjdalsdl1204@naver.com</t>
+          <t>ppghddid_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-6562</t>
+          <t>0507-1343-1828</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로 70 송도AT센터 2층 207호</t>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크101동201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/wjdalsdl1204</t>
+          <t>http://pf.kakao.com/_xcxelwK</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1341,7 +1333,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1352,22 +1344,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>246</v>
+        <v>755</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="R10" t="n">
-        <v>256</v>
+        <v>981</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1932500802</t>
+          <t>36957559</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932500802</t>
+          <t>https://m.place.naver.com/place/36957559</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1398,25 +1390,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>지금할일은네일로 송도점</t>
+          <t>언니솜씨 송도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1322-1498</t>
+          <t>032-832-4177</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 1층 193호</t>
+          <t>인천광역시 연수구 아트센터대로97번길 30 근린상가 106호 언니솜씨</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hong_nailshop</t>
+          <t>https://www.instagram.com/sister__nail__</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,13 +1443,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="R11" t="n">
-        <v>253</v>
+        <v>396</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1466,17 +1458,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1834821209</t>
+          <t>1559564560</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834821209</t>
+          <t>https://m.place.naver.com/place/1559564560</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1480,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일 109 송도점</t>
+          <t>스튜디오에텡</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nail_109@naver.com</t>
+          <t>studio_etein@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1319-1218</t>
+          <t>0507-1335-0210</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 131 여름동 149호</t>
+          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_109</t>
+          <t>https://blog.naver.com/studio_etein/224234215441</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1545,13 +1537,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>414</v>
+        <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>481</v>
+        <v>18</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1560,17 +1552,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1414664528</t>
+          <t>2046081988</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1414664528</t>
+          <t>https://m.place.naver.com/place/2046081988</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1582,25 +1574,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일바이뚜</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>네일포레</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nail_foret@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1340-2987</t>
+          <t>0507-1335-3598</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 상가 2층 221</t>
+          <t>인천광역시 연수구 인천타워대로 257 아트포레 C동 102호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_ddu</t>
+          <t>https://blog.naver.com/nail_foret</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1615,7 +1611,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1635,13 +1631,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="R13" t="n">
-        <v>269</v>
+        <v>413</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1646,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1515520159</t>
+          <t>1709958460</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1515520159</t>
+          <t>https://m.place.naver.com/place/1709958460</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1672,30 +1668,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일모아나</t>
+          <t>하꼼네일 파고드는발톱 문제성발톱 발각질</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1403-1161</t>
+          <t>0507-1364-7451</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 232 GATE , E1 1층</t>
+          <t>인천광역시 연수구 송도과학로27번길 55 A동 2층 208호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmoana_</t>
+          <t>http://pf.kakao.com/_wvvmG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1716,7 +1712,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1725,13 +1721,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1740,17 +1736,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1865551764</t>
+          <t>1024262947</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865551764</t>
+          <t>https://m.place.naver.com/place/1024262947</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1762,25 +1758,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>유데이네일</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Pausa nail artment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cheoone_@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1460-2465</t>
+          <t>0507-1465-3039</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설동 132호</t>
+          <t>인천광역시 연수구 인천타워대로 257 송도아트포레 1층 137호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yud_nail7/</t>
+          <t>https://instagram.com/pausa_nail.artment?igshid=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1830,17 +1830,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2042349151</t>
+          <t>1410434423</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042349151</t>
+          <t>https://m.place.naver.com/place/1410434423</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>차차뷰티네일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>송도네일무아</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>babbab123-@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1345-2926</t>
+          <t>0507-1305-5796</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 B동 239호</t>
+          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드,G동 상가 1층 43호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://instagram.com/chachabt_1</t>
+          <t>https://www.instagram.com/nail_mua_songdo?igsh=MWt6d3U1bjk1NzQweg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1905,13 +1909,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>276</v>
+        <v>151</v>
       </c>
       <c r="Q16" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>354</v>
+        <v>161</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1920,17 +1924,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1945183541</t>
+          <t>2036597442</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945183541</t>
+          <t>https://m.place.naver.com/place/2036597442</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1942,30 +1946,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>누오네일</t>
+          <t>무이트네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1481-2504</t>
+          <t>0507-1301-1100</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 165-17 2층 231호</t>
+          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 A동 128호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rJBWG</t>
+          <t>https://www.instagram.com/muit_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1995,13 +1999,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="Q17" t="n">
         <v>11</v>
       </c>
       <c r="R17" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2010,17 +2014,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1196589400</t>
+          <t>2019520350</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1196589400</t>
+          <t>https://m.place.naver.com/place/2019520350</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2032,25 +2036,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일에르</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>그린닷네일 뷰티</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>palette_j_1107@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1412-8155</t>
+          <t>0507-1351-8538</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 2층 211호</t>
+          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___aile/?next=undefined&amp;hl=ko</t>
+          <t>https://www.instagram.com/grin.dot_nail/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2085,13 +2093,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R18" t="n">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2100,17 +2108,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2024964834</t>
+          <t>1912589928</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024964834</t>
+          <t>https://m.place.naver.com/place/1912589928</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2122,25 +2130,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>무이트네일</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>순수네일 송도</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rlarkgo1991@naver.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1301-1100</t>
+          <t>0507-1334-1809</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 A동 128호</t>
+          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 B동 125호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muit_nail</t>
+          <t>https://blog.naver.com/rlarkgo1991</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2155,7 +2167,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2175,13 +2187,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>70</v>
+        <v>360</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="R19" t="n">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2190,17 +2202,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2019520350</t>
+          <t>1265228777</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019520350</t>
+          <t>https://m.place.naver.com/place/1265228777</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2212,30 +2224,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>로베네일</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>네일 그리다</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>nailgrida_@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1424-7675</t>
+          <t>0507-1310-1421</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 365 C동 2층 207호 로베네일</t>
+          <t>인천광역시 연수구 해돋이로 107 퍼스트월드 H동 1층 25-1호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lovae_nail</t>
+          <t>http://pf.kakao.com/_XRMxjT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2256,7 +2272,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2265,13 +2281,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R20" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2280,17 +2296,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2044125264</t>
+          <t>1953707821</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044125264</t>
+          <t>https://m.place.naver.com/place/1953707821</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2302,29 +2318,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>bonyi-@naver.com</t>
-        </is>
-      </c>
+          <t>폼</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1317-7310</t>
+          <t>032-446-2222</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
+          <t>인천광역시 연수구 랜드마크로 160 마리나베이 후문 미송초 건너편 1층 상가</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/podlab_songdo/</t>
+          <t>https://www.instagram.com/porm_songdo</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2359,13 +2371,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>652</v>
+        <v>312</v>
       </c>
       <c r="Q21" t="n">
-        <v>392</v>
+        <v>31</v>
       </c>
       <c r="R21" t="n">
-        <v>1044</v>
+        <v>343</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2374,17 +2386,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1701093046</t>
+          <t>1272387955</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701093046</t>
+          <t>https://m.place.naver.com/place/1272387955</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2396,29 +2408,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일뮤 네일&amp;패디</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sharue_88@naver.com</t>
-        </is>
-      </c>
+          <t>유데이네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1449-0613</t>
+          <t>0507-1460-2465</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
+          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설동 132호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://instagram.com/nail._.meow</t>
+          <t>https://www.instagram.com/yud_nail7/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2453,13 +2461,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1490</v>
+        <v>86</v>
       </c>
       <c r="Q22" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1600</v>
+        <v>89</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2468,17 +2476,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1446087577</t>
+          <t>2042349151</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446087577</t>
+          <t>https://m.place.naver.com/place/2042349151</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2490,29 +2498,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>발라발라네일 송도점</t>
+          <t>네일이끌림</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ballaballa0-7-0-2@naver.com</t>
+          <t>luxury24@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1408-9365</t>
+          <t>0507-1464-4142</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 A동 133호</t>
+          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티오피스텔상가204동2층220호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+          <t>https://www.instagram.com/nail_2ggellim</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2527,7 +2535,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2547,13 +2555,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>275</v>
+        <v>578</v>
       </c>
       <c r="Q23" t="n">
-        <v>296</v>
+        <v>99</v>
       </c>
       <c r="R23" t="n">
-        <v>571</v>
+        <v>677</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2562,17 +2570,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>933071487</t>
+          <t>1369252408</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/933071487</t>
+          <t>https://m.place.naver.com/place/1369252408</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2584,34 +2592,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일퀸 송도점</t>
+          <t>오빛나네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>seulbi8607@naver.com</t>
+          <t>jjw_1117@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1364-8343</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 165 2층</t>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 A동 3층 317호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_PgXfn</t>
+          <t>https://www.instagram.com/obitna_nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2632,7 +2636,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2641,13 +2645,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>49</v>
+        <v>623</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="R24" t="n">
-        <v>56</v>
+        <v>791</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2656,17 +2660,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1969782774</t>
+          <t>1076777712</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1969782774</t>
+          <t>https://m.place.naver.com/place/1076777712</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2678,34 +2682,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>하꼼네일 파고드는발톱 문제성발톱 발각질</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>maesa01@naver.com</t>
-        </is>
-      </c>
+          <t>러브윤네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1364-7451</t>
+          <t>032-815-3399</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 55 A동 2층 208호</t>
+          <t>인천광역시 연수구 송도국제대로 261 더샵 센트럴시티 217동 상가 1층 118호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_wvvmG</t>
+          <t>https://www.instagram.com/luvyun_nail?igsh=MTB5dnRza3I1czVydA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="R25" t="n">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2750,17 +2750,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1024262947</t>
+          <t>1231000131</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024262947</t>
+          <t>https://m.place.naver.com/place/1231000131</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2772,34 +2772,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>러브윤네일</t>
+          <t>나다운네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kyj_lovely@naver.com</t>
+          <t>xau123@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>032-815-3399</t>
+          <t>0507-1376-9480</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 261 더샵 센트럴시티 217동 상가 1층 118호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 3층 315호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luvyun_nail?igsh=MTB5dnRza3I1czVydA%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_YRZMs</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2820,7 +2820,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>231</v>
+        <v>12</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1231000131</t>
+          <t>1120623548</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231000131</t>
+          <t>https://m.place.naver.com/place/1120623548</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2866,34 +2866,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>연주뷰티</t>
+          <t>피치스네일 송도점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ods06060@naver.com</t>
+          <t>peaches_nail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1495-0793</t>
+          <t>0507-1363-8301</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로6번길 7 성지리벨루스 상가 2층 201호</t>
+          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeon_ju_bty?igsh=MXJldDdweXgxNml2dA%3D%3D&amp;utm_source=qr</t>
+          <t>https://peachesnail.co.kr/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2914,7 +2914,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>349</v>
+        <v>403</v>
       </c>
       <c r="Q27" t="n">
-        <v>71</v>
+        <v>701</v>
       </c>
       <c r="R27" t="n">
-        <v>420</v>
+        <v>1104</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1902277385</t>
+          <t>1241378115</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902277385</t>
+          <t>https://m.place.naver.com/place/1241378115</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2960,34 +2960,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>피치스네일 송도점</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>peaches_nail@naver.com</t>
-        </is>
-      </c>
+          <t>네일모아나</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1363-8301</t>
+          <t>0507-1403-1161</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
+          <t>인천광역시 연수구 센트럴로 232 GATE , E1 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://peachesnail.co.kr/</t>
+          <t>https://www.instagram.com/nailmoana_</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2997,7 +2993,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3008,7 +3004,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3017,13 +3013,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>402</v>
+        <v>138</v>
       </c>
       <c r="Q28" t="n">
-        <v>701</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>1103</v>
+        <v>143</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3032,17 +3028,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1241378115</t>
+          <t>1865551764</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241378115</t>
+          <t>https://m.place.naver.com/place/1865551764</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3054,29 +3050,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스튜디오에텡</t>
+          <t>비네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>studio_etein@naver.com</t>
+          <t>bi__nail@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1335-0210</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
+          <t>인천광역시 연수구 송도과학로27번길 27 203동 C221</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studio_etein/224234215441</t>
+          <t>https://blog.naver.com/bi__nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3111,13 +3103,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3126,17 +3118,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2046081988</t>
+          <t>2030460161</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046081988</t>
+          <t>https://m.place.naver.com/place/2030460161</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3148,29 +3140,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>몰튼네일</t>
+          <t>오뉴월뷰티</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ivygreentee@naver.com</t>
+          <t>vanilla__-@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1413-7890</t>
+          <t>0507-1338-4181</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 판매시설동 1층 148호</t>
+          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/molten_nailmood?igsh=MW9ob3V5dnYzM3F1aQ%3D%3D&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/onewwol_bty</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3205,13 +3197,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>349</v>
+        <v>702</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="R30" t="n">
-        <v>380</v>
+        <v>874</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3220,17 +3212,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>36307393</t>
+          <t>1572480675</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36307393</t>
+          <t>https://m.place.naver.com/place/1572480675</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3242,29 +3234,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>언니솜씨 송도점</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>jornardan@naver.com</t>
-        </is>
-      </c>
+          <t>네일르헤브</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>032-832-4177</t>
+          <t>0507-1363-9064</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로97번길 30 근린상가 106호 언니솜씨</t>
+          <t>인천광역시 연수구 컨벤시아대로 116 145호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sister__nail__</t>
+          <t>https://www.instagram.com/nail_le_reve</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3299,13 +3287,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="Q31" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>396</v>
+        <v>121</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3314,17 +3302,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1559564560</t>
+          <t>1359293825</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559564560</t>
+          <t>https://m.place.naver.com/place/1359293825</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3336,34 +3324,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>러브빈네일</t>
+          <t>송도네일송도속눈썹 모요네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dpflswlsgur7@naver.com</t>
+          <t>wldms9369@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1402-0544</t>
+          <t>0507-1317-5733</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 송도호반써밋 상가 2층 233호</t>
+          <t>인천광역시 연수구 센트럴로 313 A동 218호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luvvin_nail</t>
+          <t>http://pf.kakao.com/_GyhrG</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3384,7 +3372,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3393,13 +3381,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>125</v>
+        <v>383</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>126</v>
+        <v>387</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3408,17 +3396,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1023244566</t>
+          <t>1202013138</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023244566</t>
+          <t>https://m.place.naver.com/place/1202013138</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3430,29 +3418,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>수블링네일 인천송도점</t>
+          <t>아티카네일 송도</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>share_story_632@naver.com</t>
+          <t>atticanail@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1330-8567</t>
+          <t>0507-1355-9531</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 C동 260호</t>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크 C동 2층 258호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/subling_songdo</t>
+          <t>https://blog.naver.com/atticanail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3467,7 +3455,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3478,7 +3466,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3487,13 +3475,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="R33" t="n">
-        <v>115</v>
+        <v>341</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3502,17 +3490,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1209855396</t>
+          <t>1192730169</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209855396</t>
+          <t>https://m.place.naver.com/place/1192730169</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3524,29 +3512,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>운디아르</t>
+          <t>네일은예쁘게</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ultimateworldtravel@naver.com</t>
+          <t>beautifulnail_day@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1388-8519</t>
+          <t>0507-1324-0261</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A124</t>
+          <t>인천광역시 연수구 컨벤시아대로 50 푸르지오월드마크1단지 118호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/undiar_nail_atelier/</t>
+          <t>http://www.instagram.com/beautifulnail_day</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3581,13 +3569,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R34" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3596,17 +3584,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2073953295</t>
+          <t>1923525963</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2073953295</t>
+          <t>https://m.place.naver.com/place/1923525963</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3618,34 +3606,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>뤼미에트네일</t>
+          <t>모드니네일 송도점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hbs2002i@naver.com</t>
+          <t>dkaktsk03@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1347-2495</t>
+          <t>0507-1318-7860</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 연구단지로55번길 16 2층 210호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhgxgxon</t>
+          <t>https://blog.naver.com/dkaktsk03</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3655,7 +3643,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3666,7 +3654,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3675,13 +3663,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>52</v>
+        <v>370</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R35" t="n">
-        <v>52</v>
+        <v>386</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3690,17 +3678,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2019651969</t>
+          <t>1313369427</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019651969</t>
+          <t>https://m.place.naver.com/place/1313369427</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3712,25 +3700,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>모찌네일</t>
+          <t>몰튼네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>denise1003@naver.com</t>
+          <t>ivygreentee@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1413-7890</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 C동 4층 410호</t>
+          <t>인천광역시 연수구 센트럴로 160 판매시설동 1층 148호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mochinail_eb</t>
+          <t>https://www.instagram.com/molten_nailmood?igsh=MW9ob3V5dnYzM3F1aQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3765,13 +3757,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>152</v>
+        <v>349</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="R36" t="n">
-        <v>169</v>
+        <v>380</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3780,17 +3772,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1205962180</t>
+          <t>36307393</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205962180</t>
+          <t>https://m.place.naver.com/place/36307393</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3802,29 +3794,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pausa nail artment</t>
+          <t>러브빈네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cheoone_@naver.com</t>
+          <t>dpflswlsgur7@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1465-3039</t>
+          <t>0507-1402-0544</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 송도아트포레 1층 137호</t>
+          <t>인천광역시 연수구 랜드마크로 20 송도호반써밋 상가 2층 233호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://instagram.com/pausa_nail.artment?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>https://www.instagram.com/luvvin_nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3859,13 +3851,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3874,17 +3866,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1410434423</t>
+          <t>1023244566</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1410434423</t>
+          <t>https://m.place.naver.com/place/1023244566</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3896,29 +3888,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>반디인하우스 송도점</t>
+          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bandinhouse_songdo@naver.com</t>
+          <t>bal-eul@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1434-8241</t>
+          <t>0507-1397-2100</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
+          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bandinhouse_songdo</t>
+          <t>https://blog.naver.com/bal-eul</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3944,7 +3936,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3953,13 +3945,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="Q38" t="n">
-        <v>72</v>
+        <v>425</v>
       </c>
       <c r="R38" t="n">
-        <v>342</v>
+        <v>543</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3968,17 +3960,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1592116315</t>
+          <t>1837101349</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1592116315</t>
+          <t>https://m.place.naver.com/place/1837101349</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3990,29 +3982,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일도맑음</t>
+          <t>힐링네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dusgml-91@naver.com</t>
+          <t>lovekeiti@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1370-8213</t>
+          <t>0507-1330-2935</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 1층 166호 리치센트럴</t>
+          <t>인천광역시 연수구 해돋이로 107 G동 1층 상가56호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_malkum</t>
+          <t>https://www.instagram.com/healing08_nail/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4047,13 +4039,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>440</v>
+        <v>59</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R39" t="n">
-        <v>462</v>
+        <v>69</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4062,17 +4054,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1724575080</t>
+          <t>35051773</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1724575080</t>
+          <t>https://m.place.naver.com/place/35051773</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4084,29 +4076,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일르헤브</t>
+          <t>발라발라네일 송도점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>todaysarangtoday@naver.com</t>
+          <t>ballaballa0-7-0-2@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1363-9064</t>
+          <t>0507-1408-9365</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 116 145호</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 A동 133호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le_reve</t>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4121,7 +4113,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4141,13 +4133,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>115</v>
+        <v>275</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>296</v>
       </c>
       <c r="R40" t="n">
-        <v>121</v>
+        <v>571</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4156,17 +4148,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1359293825</t>
+          <t>933071487</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359293825</t>
+          <t>https://m.place.naver.com/place/933071487</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4178,30 +4170,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일이루나 타임스페이스</t>
+          <t>지금할일은네일로 송도점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>minyoung5959@naver.com</t>
+          <t>sym_ja@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1322-1498</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 C동 307호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 1층 193호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txdhKG</t>
+          <t>https://www.instagram.com/hong_nailshop</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4222,7 +4218,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4231,13 +4227,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="Q41" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="R41" t="n">
-        <v>504</v>
+        <v>253</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4246,17 +4242,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1227897061</t>
+          <t>1834821209</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1227897061</t>
+          <t>https://m.place.naver.com/place/1834821209</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4268,34 +4264,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일포레</t>
+          <t>오벨리뷰티 레푸스 송도점&amp;내성발톱 문제성발 발각질</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>nail_foret@naver.com</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>ehdgml320@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>refuss02@tatek.co.kr</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1335-3598</t>
+          <t>0507-1355-7923</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 아트포레 C동 102호</t>
+          <t>인천광역시 연수구 하모니로138번길 11 캐슬센트럴파크 101동 212호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_foret</t>
+          <t>http://www.refuss.co.kr/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4316,7 +4316,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="Q42" t="n">
-        <v>215</v>
+        <v>59</v>
       </c>
       <c r="R42" t="n">
-        <v>413</v>
+        <v>137</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4340,17 +4340,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1709958460</t>
+          <t>1748372244</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709958460</t>
+          <t>https://m.place.naver.com/place/1748372244</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4362,38 +4362,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오벨리뷰티 레푸스 송도점&amp;내성발톱 문제성발 발각질</t>
+          <t>더나은네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ehdgml320@naver.com</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>refuss02@tatek.co.kr</t>
-        </is>
-      </c>
+          <t>merryyear09@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1355-7923</t>
+          <t>0507-1485-4141</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 캐슬센트럴파크 101동 212호</t>
+          <t>인천광역시 연수구 컨벤시아대로 50 1단지 1층 114호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.refuss.co.kr/</t>
+          <t>https://qr.kakao.com/talk/7cbEXWNK0rWftgZp4g4Uaq8oJKc-</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4403,7 +4399,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4414,7 +4410,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4423,13 +4419,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="R43" t="n">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4438,17 +4434,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1748372244</t>
+          <t>36643790</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748372244</t>
+          <t>https://m.place.naver.com/place/36643790</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4460,29 +4456,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>나다운네일</t>
+          <t>김소형네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>xau123@naver.com</t>
+          <t>hcl9207@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1376-9480</t>
+          <t>0507-1374-3322</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 3층 315호</t>
+          <t>인천광역시 연수구 해돋이로 161 세종프라자 103호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YRZMs</t>
+          <t>https://www.instagram.com/p/B0qqrMQg9L1/?igshid=i4dcis0v7xyx</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4497,7 +4493,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4508,7 +4504,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4517,13 +4513,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>8</v>
+        <v>318</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="R44" t="n">
-        <v>12</v>
+        <v>447</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4532,17 +4528,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1120623548</t>
+          <t>1850651021</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120623548</t>
+          <t>https://m.place.naver.com/place/1850651021</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4554,29 +4550,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>bal-eul@naver.com</t>
-        </is>
-      </c>
+          <t>운디아르</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1397-2100</t>
+          <t>0507-1388-8519</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A124</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bal-eul</t>
+          <t>https://www.instagram.com/undiar_nail_atelier/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4591,7 +4583,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4611,13 +4603,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="Q45" t="n">
-        <v>425</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
-        <v>543</v>
+        <v>129</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4626,17 +4618,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1837101349</t>
+          <t>2073953295</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837101349</t>
+          <t>https://m.place.naver.com/place/2073953295</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4648,25 +4640,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>비네일</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>bi__nail@naver.com</t>
-        </is>
-      </c>
+          <t>데이지네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1444-9334</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 27 203동 C221</t>
+          <t>인천광역시 연수구 하모니로 144 A동 2층 213호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bi__nail</t>
+          <t>https://open.kakao.com/o/sKSaW3Sg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4681,7 +4673,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4701,13 +4693,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4716,17 +4708,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2030460161</t>
+          <t>1462227411</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030460161</t>
+          <t>https://m.place.naver.com/place/1462227411</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4738,29 +4730,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>발라발라네일스파 국제업무지구역점</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ballaballa0-7-0-2@naver.com</t>
-        </is>
-      </c>
+          <t>이소뉴네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1388-1058</t>
+          <t>0507-1362-4124</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 한라씨워크B동334호 발라발라네일스파</t>
+          <t>인천광역시 연수구 컨벤시아대로42번길 25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+          <t>https://www.instagram.com/aesonue_nail/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4775,7 +4763,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4791,17 +4779,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="Q47" t="n">
-        <v>273</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>413</v>
+        <v>25</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4810,17 +4798,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1290046405</t>
+          <t>1542979841</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290046405</t>
+          <t>https://m.place.naver.com/place/1542979841</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4820,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>여우손톱</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ckdwnrewq@naver.com</t>
-        </is>
-      </c>
+          <t>후쓰네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1321-6532</t>
+          <t>0507-1436-7955</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로125번길 13 아크리아1</t>
+          <t>인천광역시 연수구 해돋이로 107 더샵 퍼스트월드 H동 11호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ckdwnrewq</t>
+          <t>http://pf.kakao.com/_WinDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4869,7 +4853,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4880,7 +4864,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4889,13 +4873,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>575</v>
+        <v>230</v>
       </c>
       <c r="Q48" t="n">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="R48" t="n">
-        <v>776</v>
+        <v>252</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4904,17 +4888,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>21216458</t>
+          <t>798831444</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21216458</t>
+          <t>https://m.place.naver.com/place/798831444</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4926,29 +4910,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>모드니네일 송도점</t>
+          <t>네일뮤 네일&amp;패디</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dkaktsk03@naver.com</t>
+          <t>sharue_88@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1318-7860</t>
+          <t>0507-1449-0613</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
+          <t>인천광역시 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dkaktsk03</t>
+          <t>https://instagram.com/nail._.meow</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4963,7 +4947,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4983,13 +4967,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>370</v>
+        <v>1491</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="R49" t="n">
-        <v>386</v>
+        <v>1601</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4998,17 +4982,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1313369427</t>
+          <t>1446087577</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1313369427</t>
+          <t>https://m.place.naver.com/place/1446087577</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5020,29 +5004,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>힐링네일</t>
+          <t>이로울뷰티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>lovekeiti@naver.com</t>
+          <t>iroulbeauty@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1330-2935</t>
+          <t>0507-1420-8565</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 G동 1층 상가56호</t>
+          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healing08_nail/</t>
+          <t>https://www.instagram.com/iiroul.nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5077,13 +5061,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>59</v>
+        <v>850</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>524</v>
       </c>
       <c r="R50" t="n">
-        <v>69</v>
+        <v>1374</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5092,17 +5076,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>35051773</t>
+          <t>1745367791</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35051773</t>
+          <t>https://m.place.naver.com/place/1745367791</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5114,29 +5098,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>순수네일 송도</t>
+          <t>로베네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>rlarkgo1991@naver.com</t>
+          <t>dkfzhdspdlf@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1334-1809</t>
+          <t>0507-1424-7675</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 B동 125호</t>
+          <t>인천광역시 연수구 인천타워대로 365 C동 2층 207호 로베네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarkgo1991</t>
+          <t>https://www.instagram.com/lovae_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5151,7 +5135,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5162,7 +5146,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5171,13 +5155,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>360</v>
+        <v>116</v>
       </c>
       <c r="Q51" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>444</v>
+        <v>116</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5186,17 +5170,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1265228777</t>
+          <t>2044125264</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265228777</t>
+          <t>https://m.place.naver.com/place/2044125264</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5208,34 +5192,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>송도네일송도속눈썹 모요네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>wldms9369@naver.com</t>
-        </is>
-      </c>
+          <t>네일르블랑</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1317-5733</t>
+          <t>0507-1306-8906</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 A동 218호</t>
+          <t>인천광역시 연수구 인천타워대로 393 305동 1층 A동 112호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GyhrG</t>
+          <t>https://www.instagram.com/nail_le_blanc</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5256,7 +5236,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5265,13 +5245,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>383</v>
+        <v>19</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>387</v>
+        <v>19</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5280,17 +5260,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1202013138</t>
+          <t>2085102425</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202013138</t>
+          <t>https://m.place.naver.com/place/2085102425</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5302,34 +5282,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>인어뷰티 송도점</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>in_awe_beauty@naver.com</t>
-        </is>
-      </c>
+          <t>수블링네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1397-2403</t>
+          <t>0507-1330-8567</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
+          <t>인천광역시 연수구 센트럴로 313 C동 260호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/in.awe.beauty</t>
+          <t>https://www.instagram.com/subling_songdo</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5339,7 +5315,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5359,13 +5335,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>666</v>
+        <v>113</v>
       </c>
       <c r="Q53" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>796</v>
+        <v>115</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5374,17 +5350,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1323913451</t>
+          <t>1209855396</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323913451</t>
+          <t>https://m.place.naver.com/place/1209855396</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5396,29 +5372,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일뮬</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>catrabbit18@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이뚜</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1474-2412</t>
+          <t>0507-1340-2987</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 상가 2층 221</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_by_ddu</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5453,13 +5425,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="Q54" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="R54" t="n">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5468,17 +5440,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1415557011</t>
+          <t>1515520159</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1415557011</t>
+          <t>https://m.place.naver.com/place/1515520159</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5490,34 +5462,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>김소형네일</t>
+          <t>여우손톱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hcl9207@naver.com</t>
+          <t>ckdwnrewq@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1374-3322</t>
+          <t>0507-1321-6532</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 161 세종프라자 103호</t>
+          <t>인천광역시 연수구 신송로125번길 13 아크리아1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/B0qqrMQg9L1/?igshid=i4dcis0v7xyx</t>
+          <t>https://blog.naver.com/ckdwnrewq</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5547,13 +5519,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>318</v>
+        <v>574</v>
       </c>
       <c r="Q55" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="R55" t="n">
-        <v>447</v>
+        <v>775</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5562,17 +5534,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1850651021</t>
+          <t>21216458</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850651021</t>
+          <t>https://m.place.naver.com/place/21216458</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5584,29 +5556,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>그린닷네일 뷰티</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>palette_j_1107@naver.com</t>
-        </is>
-      </c>
+          <t>모모네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1351-8538</t>
+          <t>0507-1449-3429</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
+          <t>인천광역시 연수구 컨벤시아대로274번길 55 상가동 1층 6호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grin.dot_nail/</t>
+          <t>https://www.instagram.com/__momo.nail</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5641,13 +5609,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5656,17 +5624,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1912589928</t>
+          <t>1312635729</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912589928</t>
+          <t>https://m.place.naver.com/place/1312635729</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5678,29 +5646,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>아티카네일 송도</t>
+          <t>네일 109 송도점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>atticanail@naver.com</t>
+          <t>nail_109@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1355-9531</t>
+          <t>0507-1319-1218</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 한라씨워크 C동 2층 258호</t>
+          <t>인천광역시 연수구 아트센터대로 131 여름동 149호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atticanail</t>
+          <t>https://blog.naver.com/nail_109</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5735,13 +5703,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>222</v>
+        <v>415</v>
       </c>
       <c r="Q57" t="n">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="R57" t="n">
-        <v>341</v>
+        <v>482</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5750,17 +5718,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1192730169</t>
+          <t>1414664528</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192730169</t>
+          <t>https://m.place.naver.com/place/1414664528</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5772,29 +5740,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>모모네일 인천송도점</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>yangereek92@naver.com</t>
-        </is>
-      </c>
+          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1449-3429</t>
+          <t>0507-1317-7310</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로274번길 55 상가동 1층 6호</t>
+          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__momo.nail</t>
+          <t>https://www.instagram.com/podlab_songdo/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5829,13 +5793,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>168</v>
+        <v>652</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="R58" t="n">
-        <v>169</v>
+        <v>1044</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5844,17 +5808,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1312635729</t>
+          <t>1701093046</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312635729</t>
+          <t>https://m.place.naver.com/place/1701093046</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5866,29 +5830,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일포유</t>
+          <t>네일라벨르 송도타임스페이스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>nail_for_u@naver.com</t>
+          <t>join9360@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1374-7708</t>
+          <t>0507-1362-9360</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 122 107호 네일포유</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 314호 네일라벨르</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailforyou_/</t>
+          <t>https://blog.naver.com/join9360</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5903,7 +5867,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5914,7 +5878,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5923,13 +5887,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>48</v>
+        <v>1288</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R59" t="n">
-        <v>56</v>
+        <v>1302</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5938,17 +5902,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>36177492</t>
+          <t>1280755213</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36177492</t>
+          <t>https://m.place.naver.com/place/1280755213</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5960,25 +5924,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>오빛나네일</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>jjw_1117@naver.com</t>
-        </is>
-      </c>
+          <t>네일포유</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1374-7708</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 A동 3층 317호</t>
+          <t>인천광역시 연수구 신송로 122 107호 네일포유</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/obitna_nail</t>
+          <t>https://www.instagram.com/nailforyou_/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6013,13 +5977,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>623</v>
+        <v>48</v>
       </c>
       <c r="Q60" t="n">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="R60" t="n">
-        <v>790</v>
+        <v>56</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6028,17 +5992,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1076777712</t>
+          <t>36177492</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1076777712</t>
+          <t>https://m.place.naver.com/place/36177492</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6050,25 +6014,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일1607</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>darara5670@naver.com</t>
-        </is>
-      </c>
+          <t>네일민</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
+          <t>인천광역시 연수구 컨벤시아대로 116 푸르지오월드마크7단지 1층 125호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail160_7</t>
+          <t>https://www.instagram.com/Nail_Minae</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6094,7 +6054,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6103,13 +6063,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>446</v>
+        <v>301</v>
       </c>
       <c r="Q61" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="R61" t="n">
-        <v>477</v>
+        <v>346</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6118,17 +6078,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1249527516</t>
+          <t>1769913626</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249527516</t>
+          <t>https://m.place.naver.com/place/1769913626</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6140,12 +6100,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>송도네일에디크 센트럴점</t>
+          <t>모찌네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sym_ja@naver.com</t>
+          <t>denise1003@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -6153,17 +6113,17 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 185 센트럴비즈한라 2층 213일부호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 C동 4층 410호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_psxeCn</t>
+          <t>https://www.instagram.com/mochinail_eb</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6184,7 +6144,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6193,13 +6153,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="Q62" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R62" t="n">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6208,17 +6168,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1035124007</t>
+          <t>1205962180</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035124007</t>
+          <t>https://m.place.naver.com/place/1205962180</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6230,29 +6190,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일은예쁘게</t>
+          <t>하이피네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>beautifulnail_day@naver.com</t>
+          <t>hy_p_nail@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1324-0261</t>
+          <t>0507-1365-6641</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 50 푸르지오월드마크1단지 118호</t>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 오피스텔동 107호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beautifulnail_day</t>
+          <t>https://www.instagram.com/hy_p_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6287,13 +6247,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6302,17 +6262,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1923525963</t>
+          <t>1213017361</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1923525963</t>
+          <t>https://m.place.naver.com/place/1213017361</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6324,34 +6284,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>오뉴월뷰티</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>vanilla__-@naver.com</t>
-        </is>
-      </c>
+          <t>송도네일에디크 센트럴점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1338-4181</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
+          <t>인천광역시 연수구 인천타워대로 185 센트럴비즈한라 2층 213일부호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/onewwol_bty</t>
+          <t>http://pf.kakao.com/_psxeCn</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6372,7 +6324,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6381,13 +6333,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>700</v>
+        <v>115</v>
       </c>
       <c r="Q64" t="n">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="R64" t="n">
-        <v>872</v>
+        <v>129</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6396,17 +6348,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1572480675</t>
+          <t>1035124007</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572480675</t>
+          <t>https://m.place.naver.com/place/1035124007</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6418,29 +6370,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>볼네일 인천송도점</t>
+          <t>문제성발관리센터 메디푸스 내성발톱 무좀 각질 문제성발톱</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ballnail-@naver.com</t>
+          <t>medifuss@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1341-0638</t>
+          <t>0507-1321-3367</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 A동 1층 129-1호</t>
+          <t>인천광역시 연수구 아트센터대로 131 201동 213호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ballnail_</t>
+          <t>https://blog.naver.com/medifuss</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6455,7 +6407,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6475,13 +6427,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>390</v>
+        <v>264</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="R65" t="n">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6490,17 +6442,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2002201349</t>
+          <t>1696402748</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002201349</t>
+          <t>https://m.place.naver.com/place/1696402748</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6512,29 +6464,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일이끌림</t>
+          <t>다됨네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>luxury24@naver.com</t>
+          <t>a7814341@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1464-4142</t>
+          <t>032-815-9344</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티오피스텔상가204동2층220호</t>
+          <t>인천광역시 연수구 송도문화로28번길 27 호반베르디움 2차 아파트상가 2동 204호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_2ggellim</t>
+          <t>https://blog.naver.com/a7814341</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6549,7 +6501,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6569,13 +6521,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>579</v>
+        <v>128</v>
       </c>
       <c r="Q66" t="n">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="R66" t="n">
-        <v>678</v>
+        <v>144</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6584,17 +6536,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1369252408</t>
+          <t>1320993039</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369252408</t>
+          <t>https://m.place.naver.com/place/1320993039</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6606,34 +6558,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>데이지네일</t>
+          <t>반디인하우스 송도점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>a1070bbb@naver.com</t>
+          <t>bandinhouse_songdo@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1444-9334</t>
+          <t>0507-1434-8241</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 144 A동 2층 213호</t>
+          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKSaW3Sg</t>
+          <t>https://blog.naver.com/bandinhouse_songdo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6643,7 +6595,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6663,13 +6615,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>152</v>
+        <v>270</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="R67" t="n">
-        <v>155</v>
+        <v>342</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6678,17 +6630,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1462227411</t>
+          <t>1592116315</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462227411</t>
+          <t>https://m.place.naver.com/place/1592116315</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6700,34 +6652,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>피어라뷰티샵</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ppghddid_@naver.com</t>
-        </is>
-      </c>
+          <t>네일도맑음</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1343-1828</t>
+          <t>0507-1370-8213</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크101동201호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 1층 166호 리치센트럴</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcxelwK</t>
+          <t>https://www.instagram.com/naildo_malkum</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6748,7 +6696,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6757,13 +6705,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>755</v>
+        <v>441</v>
       </c>
       <c r="Q68" t="n">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="R68" t="n">
-        <v>981</v>
+        <v>463</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6772,17 +6720,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>36957559</t>
+          <t>1724575080</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36957559</t>
+          <t>https://m.place.naver.com/place/1724575080</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6794,34 +6742,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>이로울뷰티</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>iroulbeauty@naver.com</t>
-        </is>
-      </c>
+          <t>뤼미에트네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1420-8565</t>
+          <t>0507-1347-2495</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 210호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iiroul.nail</t>
+          <t>http://pf.kakao.com/_xhgxgxon</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6842,7 +6786,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6851,13 +6795,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>848</v>
+        <v>52</v>
       </c>
       <c r="Q69" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1371</v>
+        <v>52</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6866,17 +6810,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1745367791</t>
+          <t>2019651969</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745367791</t>
+          <t>https://m.place.naver.com/place/2019651969</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6888,34 +6832,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>더나은네일</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>merryyear09@naver.com</t>
-        </is>
-      </c>
+          <t>네일퀸 송도점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1485-4141</t>
+          <t>0507-1364-8343</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 50 1단지 1층 114호</t>
+          <t>인천광역시 연수구 송도국제대로 165 2층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://qr.kakao.com/talk/7cbEXWNK0rWftgZp4g4Uaq8oJKc-</t>
+          <t>http://pf.kakao.com/_PgXfn</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6936,7 +6876,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6945,13 +6885,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="Q70" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6960,17 +6900,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>36643790</t>
+          <t>1969782774</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36643790</t>
+          <t>https://m.place.naver.com/place/1969782774</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6982,34 +6922,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>후쓰네일</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>white5198@naver.com</t>
-        </is>
-      </c>
+          <t>네일1607</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1436-7955</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 더샵 퍼스트월드 H동 11호</t>
+          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WinDT</t>
+          <t>https://www.instagram.com/nail160_7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7039,13 +6971,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>230</v>
+        <v>446</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R71" t="n">
-        <v>252</v>
+        <v>477</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7054,17 +6986,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>798831444</t>
+          <t>1249527516</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/798831444</t>
+          <t>https://m.place.naver.com/place/1249527516</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7076,29 +7008,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일르블랑</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>6540067@naver.com</t>
-        </is>
-      </c>
+          <t>차차뷰티네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1306-8906</t>
+          <t>0507-1345-2926</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 393 305동 1층 A동 112호</t>
+          <t>인천광역시 연수구 센트럴로 313 B동 239호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le_blanc</t>
+          <t>http://instagram.com/chachabt_1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7133,13 +7061,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="R72" t="n">
-        <v>18</v>
+        <v>354</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7148,17 +7076,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2085102425</t>
+          <t>1945183541</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085102425</t>
+          <t>https://m.place.naver.com/place/1945183541</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7170,29 +7098,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>하이피네일</t>
+          <t>인어뷰티 송도점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>hy_p_nail@naver.com</t>
+          <t>in_awe_beauty@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1365-6641</t>
+          <t>0507-1397-2403</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로 70 송도AT센터 오피스텔동 107호</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hy_p_nail</t>
+          <t>https://www.instagram.com/in.awe.beauty</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7227,13 +7155,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>68</v>
+        <v>666</v>
       </c>
       <c r="Q73" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="R73" t="n">
-        <v>73</v>
+        <v>796</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7242,17 +7170,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1213017361</t>
+          <t>1323913451</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213017361</t>
+          <t>https://m.place.naver.com/place/1323913451</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7264,29 +7192,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일잇</t>
+          <t>비지트네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>nail__it_@naver.com</t>
+          <t>visitnail@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1401-9180</t>
+          <t>0507-1394-9422</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동314호</t>
+          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 C동 341호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail__it_</t>
+          <t>https://blog.naver.com/visitnail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7321,13 +7249,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>540</v>
+        <v>86</v>
       </c>
       <c r="Q74" t="n">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="R74" t="n">
-        <v>668</v>
+        <v>134</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7336,17 +7264,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>878464897</t>
+          <t>1503164148</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/878464897</t>
+          <t>https://m.place.naver.com/place/1503164148</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7358,25 +7286,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일민</t>
+          <t>볼네일 인천송도점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>cej909@naver.com</t>
+          <t>ballnail-@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1341-0638</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 116 푸르지오월드마크7단지 1층 125호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 A동 1층 129-1호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/Nail_Minae</t>
+          <t>https://www.instagram.com/ballnail_</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7411,13 +7343,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>301</v>
+        <v>391</v>
       </c>
       <c r="Q75" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="R75" t="n">
-        <v>346</v>
+        <v>406</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7426,17 +7358,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1769913626</t>
+          <t>2002201349</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769913626</t>
+          <t>https://m.place.naver.com/place/2002201349</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7448,29 +7380,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>비지트네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>visitnail@naver.com</t>
-        </is>
-      </c>
+          <t>앤드네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1394-9422</t>
+          <t>0507-1478-8939</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 C동 341호</t>
+          <t>인천광역시 연수구 랜드마크로 20 판매시설 2층 230호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/visitnail</t>
+          <t>https://www.instagram.com/_andnail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7485,7 +7413,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7505,13 +7433,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>86</v>
+        <v>328</v>
       </c>
       <c r="Q76" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>133</v>
+        <v>333</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7520,17 +7448,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1503164148</t>
+          <t>1327958684</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503164148</t>
+          <t>https://m.place.naver.com/place/1327958684</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/송도_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/송도_네일샵.xlsx
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일잇</t>
+          <t>피치스네일 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nail__it_@naver.com</t>
+          <t>peaches_nail@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1401-9180</t>
+          <t>0507-1363-8301</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동314호</t>
+          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail__it_</t>
+          <t>https://peachesnail.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>540</v>
+        <v>403</v>
       </c>
       <c r="Q2" t="n">
-        <v>128</v>
+        <v>698</v>
       </c>
       <c r="R2" t="n">
-        <v>668</v>
+        <v>1101</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>878464897</t>
+          <t>1241378115</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/878464897</t>
+          <t>https://m.place.naver.com/place/1241378115</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,26 +658,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일이루나 타임스페이스</t>
+          <t>운디아르</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1388-8519</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 C동 307호</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A124</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txdhKG</t>
+          <t>https://www.instagram.com/undiar_nail_atelier/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -698,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -707,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>481</v>
+        <v>124</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>504</v>
+        <v>130</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1227897061</t>
+          <t>2073953295</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1227897061</t>
+          <t>https://m.place.naver.com/place/2073953295</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -744,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일뮬</t>
+          <t>네일포레</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>catrabbit18@naver.com</t>
+          <t>nail_foret@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1474-2412</t>
+          <t>0507-1335-3598</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
+          <t>인천광역시 연수구 인천타워대로 257 아트포레 C동 102호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/nail_foret</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -781,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -801,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="Q4" t="n">
-        <v>63</v>
+        <v>215</v>
       </c>
       <c r="R4" t="n">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1415557011</t>
+          <t>1709958460</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1415557011</t>
+          <t>https://m.place.naver.com/place/1709958460</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -838,30 +842,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일에르</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>뤼미에트네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hbs2002i@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1412-8155</t>
+          <t>0507-1347-2495</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 2층 211호</t>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 210호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___aile/?next=undefined&amp;hl=ko</t>
+          <t>http://pf.kakao.com/_xhgxgxon</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -882,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -891,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2024964834</t>
+          <t>2019651969</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024964834</t>
+          <t>https://m.place.naver.com/place/2019651969</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -928,25 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>연주뷰티</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ckdwnrewq@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1495-0793</t>
+          <t>0507-1321-6532</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로6번길 7 성지리벨루스 상가 2층 201호</t>
+          <t>인천광역시 연수구 신송로125번길 13 아크리아1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeon_ju_bty?igsh=MXJldDdweXgxNml2dA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/ckdwnrewq</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -961,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -981,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>349</v>
+        <v>575</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="R6" t="n">
-        <v>420</v>
+        <v>776</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -996,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1902277385</t>
+          <t>21216458</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902277385</t>
+          <t>https://m.place.naver.com/place/21216458</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1018,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>발라발라네일스파 국제업무지구역점</t>
+          <t>수블링네일 인천송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ballaballa0-7-0-2@naver.com</t>
+          <t>share_story_632@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-1058</t>
+          <t>0507-1330-8567</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 한라씨워크B동334호 발라발라네일스파</t>
+          <t>인천광역시 연수구 센트럴로 313 C동 260호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+          <t>https://www.instagram.com/subling_songdo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1055,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1071,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>273</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>413</v>
+        <v>115</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1290046405</t>
+          <t>1209855396</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290046405</t>
+          <t>https://m.place.naver.com/place/1209855396</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1112,34 +1124,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>미니네일</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>wjdalsdl1204@naver.com</t>
-        </is>
-      </c>
+          <t>앤드네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-6562</t>
+          <t>0507-1478-8939</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로 70 송도AT센터 2층 207호</t>
+          <t>인천광역시 연수구 랜드마크로 20 판매시설 2층 230호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/wjdalsdl1204</t>
+          <t>https://www.instagram.com/_andnail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1149,7 +1157,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1165,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>246</v>
+        <v>328</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>256</v>
+        <v>333</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1932500802</t>
+          <t>1327958684</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932500802</t>
+          <t>https://m.place.naver.com/place/1327958684</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1206,25 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>누오네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>송도네일송도속눈썹 모요네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>wldms9369@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1481-2504</t>
+          <t>0507-1317-5733</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 165-17 2층 231호</t>
+          <t>인천광역시 연수구 센트럴로 313 A동 218호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rJBWG</t>
+          <t>http://pf.kakao.com/_GyhrG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>129</v>
+        <v>384</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>140</v>
+        <v>388</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1274,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1196589400</t>
+          <t>1202013138</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1196589400</t>
+          <t>https://m.place.naver.com/place/1202013138</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1296,34 +1308,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피어라뷰티샵</t>
+          <t>Pausa nail artment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ppghddid_@naver.com</t>
+          <t>cheoone_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1343-1828</t>
+          <t>0507-1465-3039</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크101동201호</t>
+          <t>인천광역시 연수구 인천타워대로 257 송도아트포레 1층 137호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcxelwK</t>
+          <t>https://instagram.com/pausa_nail.artment?igshid=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1344,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1353,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>755</v>
+        <v>106</v>
       </c>
       <c r="Q10" t="n">
-        <v>226</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>981</v>
+        <v>118</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36957559</t>
+          <t>1410434423</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36957559</t>
+          <t>https://m.place.naver.com/place/1410434423</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1390,25 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>언니솜씨 송도점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>네일은예쁘게</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>beautifulnail_day@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-832-4177</t>
+          <t>0507-1324-0261</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로97번길 30 근린상가 106호 언니솜씨</t>
+          <t>인천광역시 연수구 컨벤시아대로 50 푸르지오월드마크1단지 118호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sister__nail__</t>
+          <t>http://www.instagram.com/beautifulnail_day</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>396</v>
+        <v>62</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1458,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1559564560</t>
+          <t>1923525963</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559564560</t>
+          <t>https://m.place.naver.com/place/1923525963</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1480,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스튜디오에텡</t>
+          <t>이로울뷰티</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>studio_etein@naver.com</t>
+          <t>iroulbeauty@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1335-0210</t>
+          <t>0507-1420-8565</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
+          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studio_etein/224234215441</t>
+          <t>https://www.instagram.com/iiroul.nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1517,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1528,7 +1544,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1537,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>852</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>524</v>
       </c>
       <c r="R12" t="n">
-        <v>18</v>
+        <v>1376</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1552,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2046081988</t>
+          <t>1745367791</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046081988</t>
+          <t>https://m.place.naver.com/place/1745367791</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1574,29 +1590,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일포레</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>nail_foret@naver.com</t>
-        </is>
-      </c>
+          <t>폼</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1335-3598</t>
+          <t>032-446-2222</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 아트포레 C동 102호</t>
+          <t>인천광역시 연수구 랜드마크로 160 마리나베이 후문 미송초 건너편 1층 상가</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_foret</t>
+          <t>https://www.instagram.com/porm_songdo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1611,7 +1623,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1631,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>198</v>
+        <v>313</v>
       </c>
       <c r="Q13" t="n">
-        <v>215</v>
+        <v>31</v>
       </c>
       <c r="R13" t="n">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1646,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1709958460</t>
+          <t>1272387955</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709958460</t>
+          <t>https://m.place.naver.com/place/1272387955</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1668,30 +1680,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>하꼼네일 파고드는발톱 문제성발톱 발각질</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>비네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bi__nail@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1364-7451</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 55 A동 2층 208호</t>
+          <t>인천광역시 연수구 송도과학로27번길 27 203동 C221</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_wvvmG</t>
+          <t>https://blog.naver.com/bi__nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1701,7 +1713,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1721,13 +1733,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>270</v>
+        <v>84</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>275</v>
+        <v>106</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1736,17 +1748,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1024262947</t>
+          <t>2030460161</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024262947</t>
+          <t>https://m.place.naver.com/place/2030460161</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1758,34 +1770,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pausa nail artment</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>cheoone_@naver.com</t>
-        </is>
-      </c>
+          <t>네일퀸 송도점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1465-3039</t>
+          <t>0507-1364-8343</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 송도아트포레 1층 137호</t>
+          <t>인천광역시 연수구 송도국제대로 165 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://instagram.com/pausa_nail.artment?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>http://pf.kakao.com/_PgXfn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1806,7 +1814,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1815,13 +1823,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1830,17 +1838,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1410434423</t>
+          <t>1969782774</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1410434423</t>
+          <t>https://m.place.naver.com/place/1969782774</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1852,29 +1860,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>송도네일무아</t>
+          <t>연주뷰티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>babbab123-@naver.com</t>
+          <t>ods06060@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1305-5796</t>
+          <t>0507-1495-0793</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드,G동 상가 1층 43호</t>
+          <t>인천광역시 연수구 신송로6번길 7 성지리벨루스 상가 2층 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mua_songdo?igsh=MWt6d3U1bjk1NzQweg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/yeon_ju_bty?igsh=MXJldDdweXgxNml2dA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1909,13 +1917,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>151</v>
+        <v>350</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="R16" t="n">
-        <v>161</v>
+        <v>421</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1924,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2036597442</t>
+          <t>1902277385</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036597442</t>
+          <t>https://m.place.naver.com/place/1902277385</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1946,30 +1954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>무이트네일</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>네일이루나 타임스페이스</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flycrew0416@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1301-1100</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 A동 128호</t>
+          <t>인천광역시 연수구 하모니로 158 C동 307호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muit_nail</t>
+          <t>http://pf.kakao.com/_txdhKG</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1999,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>70</v>
+        <v>481</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="R17" t="n">
-        <v>81</v>
+        <v>504</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2014,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2019520350</t>
+          <t>1227897061</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019520350</t>
+          <t>https://m.place.naver.com/place/1227897061</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2036,34 +2044,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>그린닷네일 뷰티</t>
+          <t>오벨리뷰티 레푸스 송도점&amp;내성발톱 문제성발 발각질</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>palette_j_1107@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>ehdgml320@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>refuss02@tatek.co.kr</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1351-8538</t>
+          <t>0507-1355-7923</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
+          <t>인천광역시 연수구 하모니로138번길 11 캐슬센트럴파크 101동 212호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grin.dot_nail/</t>
+          <t>http://www.refuss.co.kr/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2073,7 +2085,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2084,7 +2096,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2093,13 +2105,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="R18" t="n">
-        <v>195</v>
+        <v>136</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2108,17 +2120,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1912589928</t>
+          <t>1748372244</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912589928</t>
+          <t>https://m.place.naver.com/place/1748372244</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2130,29 +2142,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>순수네일 송도</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rlarkgo1991@naver.com</t>
-        </is>
-      </c>
+          <t>차차뷰티네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1334-1809</t>
+          <t>0507-1345-2926</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 B동 125호</t>
+          <t>인천광역시 연수구 센트럴로 313 B동 239호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarkgo1991</t>
+          <t>http://instagram.com/chachabt_1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2167,7 +2175,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2178,7 +2186,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2187,13 +2195,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="Q19" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="R19" t="n">
-        <v>444</v>
+        <v>354</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2202,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1265228777</t>
+          <t>1945183541</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265228777</t>
+          <t>https://m.place.naver.com/place/1945183541</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2224,34 +2232,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일 그리다</t>
+          <t>네일잇</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nailgrida_@naver.com</t>
+          <t>nail__it_@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1310-1421</t>
+          <t>0507-1401-9180</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 퍼스트월드 H동 1층 25-1호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동314호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XRMxjT</t>
+          <t>https://blog.naver.com/nail__it_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2261,7 +2269,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2272,7 +2280,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2281,13 +2289,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>98</v>
+        <v>540</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="R20" t="n">
-        <v>132</v>
+        <v>668</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2296,17 +2304,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1953707821</t>
+          <t>878464897</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953707821</t>
+          <t>https://m.place.naver.com/place/878464897</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2318,25 +2326,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>폼</t>
+          <t>모모네일 인천송도점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>032-446-2222</t>
+          <t>0507-1449-3429</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 160 마리나베이 후문 미송초 건너편 1층 상가</t>
+          <t>인천광역시 연수구 컨벤시아대로274번길 55 상가동 1층 6호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/porm_songdo</t>
+          <t>https://www.instagram.com/__momo.nail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2371,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>312</v>
+        <v>168</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>343</v>
+        <v>169</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2386,17 +2394,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1272387955</t>
+          <t>1312635729</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272387955</t>
+          <t>https://m.place.naver.com/place/1312635729</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2408,25 +2416,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>유데이네일</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>하이피네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hy_p_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1460-2465</t>
+          <t>0507-1365-6641</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설동 132호</t>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 오피스텔동 107호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yud_nail7/</t>
+          <t>https://www.instagram.com/hy_p_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2461,13 +2473,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2476,17 +2488,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2042349151</t>
+          <t>1213017361</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042349151</t>
+          <t>https://m.place.naver.com/place/1213017361</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2498,29 +2510,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일이끌림</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>luxury24@naver.com</t>
-        </is>
-      </c>
+          <t>로베네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1464-4142</t>
+          <t>0507-1424-7675</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티오피스텔상가204동2층220호</t>
+          <t>인천광역시 연수구 인천타워대로 365 C동 2층 207호 로베네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_2ggellim</t>
+          <t>https://www.instagram.com/lovae_nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2555,13 +2563,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>578</v>
+        <v>116</v>
       </c>
       <c r="Q23" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>677</v>
+        <v>116</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2570,17 +2578,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1369252408</t>
+          <t>2044125264</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369252408</t>
+          <t>https://m.place.naver.com/place/2044125264</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2592,30 +2600,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>오빛나네일</t>
+          <t>미니네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jjw_1117@naver.com</t>
+          <t>wjdalsdl1204@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1341-6562</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 A동 3층 317호</t>
+          <t>인천광역시 연수구 송도과학로 70 송도AT센터 2층 207호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/obitna_nail</t>
+          <t>https://link.inpock.co.kr/wjdalsdl1204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2625,7 +2637,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2641,17 +2653,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>623</v>
+        <v>247</v>
       </c>
       <c r="Q24" t="n">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>791</v>
+        <v>257</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2660,17 +2672,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1076777712</t>
+          <t>1932500802</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1076777712</t>
+          <t>https://m.place.naver.com/place/1932500802</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2682,25 +2694,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>러브윤네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>네일1607</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>tammi1607@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>032-815-3399</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 261 더샵 센트럴시티 217동 상가 1층 118호</t>
+          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luvyun_nail?igsh=MTB5dnRza3I1czVydA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail160_7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2726,7 +2738,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2735,13 +2747,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>191</v>
+        <v>446</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
-        <v>231</v>
+        <v>477</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2750,17 +2762,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1231000131</t>
+          <t>1249527516</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231000131</t>
+          <t>https://m.place.naver.com/place/1249527516</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2772,34 +2784,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>나다운네일</t>
+          <t>네일 109 송도점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>xau123@naver.com</t>
+          <t>nail_109@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1376-9480</t>
+          <t>0507-1319-1218</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 3층 315호</t>
+          <t>인천광역시 연수구 아트센터대로 131 여름동 149호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YRZMs</t>
+          <t>https://blog.naver.com/nail_109</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2809,7 +2821,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2829,13 +2841,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>8</v>
+        <v>417</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="R26" t="n">
-        <v>12</v>
+        <v>484</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2844,17 +2856,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1120623548</t>
+          <t>1414664528</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120623548</t>
+          <t>https://m.place.naver.com/place/1414664528</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2866,29 +2878,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>피치스네일 송도점</t>
+          <t>후쓰네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>peaches_nail@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1363-8301</t>
+          <t>032-835-7955</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 50 웨스트동 213호</t>
+          <t>인천광역시 연수구 해돋이로 107 더샵 퍼스트월드 H동 11호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://peachesnail.co.kr/</t>
+          <t>http://pf.kakao.com/_WinDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2903,7 +2915,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2923,13 +2935,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>403</v>
+        <v>230</v>
       </c>
       <c r="Q27" t="n">
-        <v>701</v>
+        <v>22</v>
       </c>
       <c r="R27" t="n">
-        <v>1104</v>
+        <v>252</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2938,17 +2950,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1241378115</t>
+          <t>798831444</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241378115</t>
+          <t>https://m.place.naver.com/place/798831444</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2960,25 +2972,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일모아나</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>볼네일 인천송도점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ballnail-@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1403-1161</t>
+          <t>0507-1341-0638</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 232 GATE , E1 1층</t>
+          <t>인천광역시 연수구 하모니로178번길 22 A동 1층 129-1호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmoana_</t>
+          <t>https://www.instagram.com/ballnail_</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3013,13 +3029,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>138</v>
+        <v>393</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R28" t="n">
-        <v>143</v>
+        <v>408</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3028,17 +3044,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1865551764</t>
+          <t>2002201349</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865551764</t>
+          <t>https://m.place.naver.com/place/2002201349</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3050,25 +3066,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비네일</t>
+          <t>무이트네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bi__nail@naver.com</t>
+          <t>gonazzing@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1301-1100</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 27 203동 C221</t>
+          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 A동 128호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bi__nail</t>
+          <t>https://www.instagram.com/muit_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3083,7 +3103,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3103,13 +3123,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="R29" t="n">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3118,17 +3138,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2030460161</t>
+          <t>2019520350</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030460161</t>
+          <t>https://m.place.naver.com/place/2019520350</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3140,29 +3160,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>오뉴월뷰티</t>
+          <t>더나은네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>vanilla__-@naver.com</t>
+          <t>merryyear09@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1338-4181</t>
+          <t>0507-1485-4141</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
+          <t>인천광역시 연수구 컨벤시아대로 50 1단지 1층 114호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/onewwol_bty</t>
+          <t>https://qr.kakao.com/talk/7cbEXWNK0rWftgZp4g4Uaq8oJKc-</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3197,13 +3217,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>702</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="R30" t="n">
-        <v>874</v>
+        <v>43</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3212,17 +3232,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1572480675</t>
+          <t>36643790</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572480675</t>
+          <t>https://m.place.naver.com/place/36643790</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3234,25 +3254,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일르헤브</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>이소뉴네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1363-9064</t>
+          <t>0507-1362-4124</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 116 145호</t>
+          <t>인천광역시 연수구 컨벤시아대로42번길 25</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le_reve</t>
+          <t>https://www.instagram.com/aesonue_nail/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3287,13 +3311,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3302,17 +3326,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1359293825</t>
+          <t>1542979841</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359293825</t>
+          <t>https://m.place.naver.com/place/1542979841</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3324,34 +3348,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>송도네일송도속눈썹 모요네일</t>
+          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>wldms9369@naver.com</t>
+          <t>bal-eul@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1317-5733</t>
+          <t>0507-1397-2100</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 A동 218호</t>
+          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GyhrG</t>
+          <t>https://blog.naver.com/bal-eul</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3361,7 +3385,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3372,7 +3396,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3381,13 +3405,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>383</v>
+        <v>118</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>427</v>
       </c>
       <c r="R32" t="n">
-        <v>387</v>
+        <v>545</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3396,17 +3420,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1202013138</t>
+          <t>1837101349</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202013138</t>
+          <t>https://m.place.naver.com/place/1837101349</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3418,29 +3442,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아티카네일 송도</t>
+          <t>러브빈네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>atticanail@naver.com</t>
+          <t>dpflswlsgur7@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1355-9531</t>
+          <t>0507-1402-0544</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 한라씨워크 C동 2층 258호</t>
+          <t>인천광역시 연수구 랜드마크로 20 송도호반써밋 상가 2층 233호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atticanail</t>
+          <t>https://www.instagram.com/luvvin_nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3455,7 +3479,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3466,7 +3490,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3475,13 +3499,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="Q33" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>341</v>
+        <v>126</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3490,17 +3514,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1192730169</t>
+          <t>1023244566</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192730169</t>
+          <t>https://m.place.naver.com/place/1023244566</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3512,29 +3536,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일은예쁘게</t>
+          <t>네일르헤브</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>beautifulnail_day@naver.com</t>
+          <t>todaysarangtoday@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1324-0261</t>
+          <t>0507-1363-9064</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 50 푸르지오월드마크1단지 118호</t>
+          <t>인천광역시 연수구 컨벤시아대로 116 145호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beautifulnail_day</t>
+          <t>https://www.instagram.com/nail_le_reve</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3569,13 +3593,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3584,17 +3608,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1923525963</t>
+          <t>1359293825</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1923525963</t>
+          <t>https://m.place.naver.com/place/1359293825</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3606,29 +3630,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>모드니네일 송도점</t>
+          <t>네일도맑음</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dkaktsk03@naver.com</t>
+          <t>dusgml-91@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1318-7860</t>
+          <t>0507-1370-8213</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 1층 166호 리치센트럴</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dkaktsk03</t>
+          <t>https://www.instagram.com/naildo_malkum</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3643,7 +3667,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3663,13 +3687,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>370</v>
+        <v>443</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="R35" t="n">
-        <v>386</v>
+        <v>465</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3678,17 +3702,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1313369427</t>
+          <t>1724575080</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1313369427</t>
+          <t>https://m.place.naver.com/place/1724575080</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3700,29 +3724,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>몰튼네일</t>
+          <t>네일바이뚜</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ivygreentee@naver.com</t>
+          <t>byl1003@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1413-7890</t>
+          <t>0507-1340-2987</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 판매시설동 1층 148호</t>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 상가 2층 221</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/molten_nailmood?igsh=MW9ob3V5dnYzM3F1aQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_by_ddu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3757,13 +3781,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>349</v>
+        <v>217</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="R36" t="n">
-        <v>380</v>
+        <v>269</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3772,17 +3796,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>36307393</t>
+          <t>1515520159</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36307393</t>
+          <t>https://m.place.naver.com/place/1515520159</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3794,29 +3818,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>러브빈네일</t>
+          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dpflswlsgur7@naver.com</t>
+          <t>bonyi-@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1402-0544</t>
+          <t>0507-1317-7310</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 송도호반써밋 상가 2층 233호</t>
+          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luvvin_nail</t>
+          <t>https://www.instagram.com/podlab_songdo/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3851,13 +3875,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>125</v>
+        <v>652</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="R37" t="n">
-        <v>126</v>
+        <v>1044</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3866,17 +3890,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1023244566</t>
+          <t>1701093046</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023244566</t>
+          <t>https://m.place.naver.com/place/1701093046</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3888,34 +3912,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>문제성 발관리센터 발을 내성발톱 무좀 발각질 문제성발톱</t>
+          <t>송도네일에디크 센트럴점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bal-eul@naver.com</t>
+          <t>sym_ja@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1397-2100</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 A동 2층</t>
+          <t>인천광역시 연수구 인천타워대로 185 센트럴비즈한라 2층 213일부호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bal-eul</t>
+          <t>http://pf.kakao.com/_psxeCn</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3925,7 +3945,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3936,7 +3956,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3945,13 +3965,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q38" t="n">
-        <v>425</v>
+        <v>14</v>
       </c>
       <c r="R38" t="n">
-        <v>543</v>
+        <v>129</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3960,17 +3980,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1837101349</t>
+          <t>1035124007</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837101349</t>
+          <t>https://m.place.naver.com/place/1035124007</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3982,29 +4002,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>힐링네일</t>
+          <t>발라발라네일스파 국제업무지구역점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>lovekeiti@naver.com</t>
+          <t>ballaballa0-7-0-2@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1330-2935</t>
+          <t>0507-1388-1058</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 G동 1층 상가56호</t>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크B동334호 발라발라네일스파</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healing08_nail/</t>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4019,7 +4039,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4035,17 +4055,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="R39" t="n">
-        <v>69</v>
+        <v>413</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4054,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>35051773</t>
+          <t>1290046405</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35051773</t>
+          <t>https://m.place.naver.com/place/1290046405</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4076,34 +4096,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>발라발라네일 송도점</t>
+          <t>피어라뷰티샵</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ballaballa0-7-0-2@naver.com</t>
+          <t>ppghddid_@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1408-9365</t>
+          <t>0507-1343-1828</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 A동 133호</t>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크101동201호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
+          <t>http://pf.kakao.com/_xcxelwK</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4113,7 +4133,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4124,7 +4144,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4133,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>275</v>
+        <v>755</v>
       </c>
       <c r="Q40" t="n">
-        <v>296</v>
+        <v>226</v>
       </c>
       <c r="R40" t="n">
-        <v>571</v>
+        <v>981</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4148,17 +4168,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>933071487</t>
+          <t>36957559</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/933071487</t>
+          <t>https://m.place.naver.com/place/36957559</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4170,34 +4190,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>지금할일은네일로 송도점</t>
+          <t>김소형네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sym_ja@naver.com</t>
+          <t>hcl9207@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1322-1498</t>
+          <t>0507-1374-3322</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 1층 193호</t>
+          <t>인천광역시 연수구 해돋이로 161 세종프라자 103호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hong_nailshop</t>
+          <t>https://www.instagram.com/p/B0qqrMQg9L1/?igshid=i4dcis0v7xyx</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4207,7 +4227,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4227,13 +4247,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>219</v>
+        <v>318</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="R41" t="n">
-        <v>253</v>
+        <v>447</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4242,17 +4262,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1834821209</t>
+          <t>1850651021</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834821209</t>
+          <t>https://m.place.naver.com/place/1850651021</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4264,38 +4284,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>오벨리뷰티 레푸스 송도점&amp;내성발톱 문제성발 발각질</t>
+          <t>순수네일 송도</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ehdgml320@naver.com</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>refuss02@tatek.co.kr</t>
-        </is>
-      </c>
+          <t>rlarkgo1991@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1355-7923</t>
+          <t>0507-1334-1809</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 캐슬센트럴파크 101동 212호</t>
+          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 B동 125호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://www.refuss.co.kr/</t>
+          <t>https://blog.naver.com/rlarkgo1991</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4325,13 +4341,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>78</v>
+        <v>359</v>
       </c>
       <c r="Q42" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="R42" t="n">
-        <v>137</v>
+        <v>443</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4340,17 +4356,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1748372244</t>
+          <t>1265228777</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748372244</t>
+          <t>https://m.place.naver.com/place/1265228777</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4362,29 +4378,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>더나은네일</t>
+          <t>발라발라네일 송도점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>merryyear09@naver.com</t>
+          <t>ballaballa0-7-0-2@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1485-4141</t>
+          <t>0507-1408-9365</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 50 1단지 1층 114호</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 A동 133호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://qr.kakao.com/talk/7cbEXWNK0rWftgZp4g4Uaq8oJKc-</t>
+          <t>https://blog.naver.com/ballaballa0-7-0-2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4399,7 +4415,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4419,13 +4435,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="Q43" t="n">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="R43" t="n">
-        <v>43</v>
+        <v>571</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4434,17 +4450,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>36643790</t>
+          <t>933071487</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36643790</t>
+          <t>https://m.place.naver.com/place/933071487</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4456,34 +4472,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>김소형네일</t>
+          <t>네일뮤 네일&amp;패디</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>hcl9207@naver.com</t>
+          <t>sharue_88@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1374-3322</t>
+          <t>0507-1449-0613</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 161 세종프라자 103호</t>
+          <t>인천광역시 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/B0qqrMQg9L1/?igshid=i4dcis0v7xyx</t>
+          <t>https://instagram.com/nail._.meow</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4493,7 +4509,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4513,13 +4529,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>318</v>
+        <v>1492</v>
       </c>
       <c r="Q44" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="R44" t="n">
-        <v>447</v>
+        <v>1602</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4528,17 +4544,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1850651021</t>
+          <t>1446087577</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850651021</t>
+          <t>https://m.place.naver.com/place/1446087577</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4550,30 +4566,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>운디아르</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>네일 그리다</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nailgrida_@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1388-8519</t>
+          <t>0507-1310-1421</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A124</t>
+          <t>인천광역시 연수구 해돋이로 107 퍼스트월드 H동 1층 25-1호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/undiar_nail_atelier/</t>
+          <t>http://pf.kakao.com/_XRMxjT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4594,7 +4614,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4603,13 +4623,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="R45" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4618,17 +4638,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2073953295</t>
+          <t>1953707821</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2073953295</t>
+          <t>https://m.place.naver.com/place/1953707821</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4640,25 +4660,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>데이지네일</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>비지트네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>visitnail@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1444-9334</t>
+          <t>0507-1394-9422</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 144 A동 2층 213호</t>
+          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 C동 341호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKSaW3Sg</t>
+          <t>https://blog.naver.com/visitnail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4673,7 +4697,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4684,7 +4708,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4693,13 +4717,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4708,17 +4732,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1462227411</t>
+          <t>1503164148</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462227411</t>
+          <t>https://m.place.naver.com/place/1503164148</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4730,25 +4754,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>이소뉴네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>모찌네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>denise1003@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1362-4124</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로42번길 25</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 C동 4층 410호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aesonue_nail/</t>
+          <t>https://www.instagram.com/mochinail_eb</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4783,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R47" t="n">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4798,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1542979841</t>
+          <t>1205962180</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1542979841</t>
+          <t>https://m.place.naver.com/place/1205962180</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4820,30 +4844,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>후쓰네일</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>스튜디오에텡</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>studio_etein@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1436-7955</t>
+          <t>0507-1335-0210</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 더샵 퍼스트월드 H동 11호</t>
+          <t>인천광역시 연수구 인천타워대로 301 A동 2층 2026호 스튜디오 에텡</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WinDT</t>
+          <t>https://blog.naver.com/studio_etein/224234215441</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4853,7 +4881,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4873,13 +4901,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
       <c r="Q48" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4888,17 +4916,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>798831444</t>
+          <t>2046081988</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/798831444</t>
+          <t>https://m.place.naver.com/place/2046081988</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4910,34 +4938,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일뮤 네일&amp;패디</t>
+          <t>나다운네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sharue_88@naver.com</t>
+          <t>xau123@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1449-0613</t>
+          <t>0507-1376-9480</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 107 커낼워크D3 AUTUMN 302동 1층 173호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 3층 315호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://instagram.com/nail._.meow</t>
+          <t>http://pf.kakao.com/_YRZMs</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4958,7 +4986,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4967,13 +4995,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1491</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1601</v>
+        <v>12</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4982,17 +5010,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1446087577</t>
+          <t>1120623548</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446087577</t>
+          <t>https://m.place.naver.com/place/1120623548</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5004,29 +5032,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>이로울뷰티</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>iroulbeauty@naver.com</t>
-        </is>
-      </c>
+          <t>유데이네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1420-8565</t>
+          <t>0507-1460-2465</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로171번길 11 203호</t>
+          <t>인천광역시 연수구 하모니로188번길 17 근린생활시설동 132호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iiroul.nail</t>
+          <t>https://www.instagram.com/yud_nail7/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5061,13 +5085,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>850</v>
+        <v>87</v>
       </c>
       <c r="Q50" t="n">
-        <v>524</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>1374</v>
+        <v>90</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5076,17 +5100,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1745367791</t>
+          <t>2042349151</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745367791</t>
+          <t>https://m.place.naver.com/place/2042349151</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5098,29 +5122,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>로베네일</t>
+          <t>인어뷰티 송도점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>dkfzhdspdlf@naver.com</t>
+          <t>in_awe_beauty@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1424-7675</t>
+          <t>0507-1397-2403</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 365 C동 2층 207호 로베네일</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lovae_nail</t>
+          <t>https://www.instagram.com/in.awe.beauty</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5155,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>116</v>
+        <v>665</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="R51" t="n">
-        <v>116</v>
+        <v>795</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5170,17 +5194,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2044125264</t>
+          <t>1323913451</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044125264</t>
+          <t>https://m.place.naver.com/place/1323913451</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5192,25 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일르블랑</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>모드니네일 송도점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dkaktsk03@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1306-8906</t>
+          <t>0507-1318-7860</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 393 305동 1층 A동 112호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 3층 313호 모드니네일 송도점</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le_blanc</t>
+          <t>https://blog.naver.com/dkaktsk03</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5225,7 +5253,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5245,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>19</v>
+        <v>371</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R52" t="n">
-        <v>19</v>
+        <v>387</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5260,17 +5288,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2085102425</t>
+          <t>1313369427</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085102425</t>
+          <t>https://m.place.naver.com/place/1313369427</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5282,25 +5310,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>수블링네일 인천송도점</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>오빛나네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jjw_1117@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1330-8567</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 C동 260호</t>
+          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 A동 3층 317호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/subling_songdo</t>
+          <t>https://www.instagram.com/obitna_nail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5335,13 +5363,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>113</v>
+        <v>623</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="R53" t="n">
-        <v>115</v>
+        <v>795</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5350,17 +5378,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1209855396</t>
+          <t>1076777712</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209855396</t>
+          <t>https://m.place.naver.com/place/1076777712</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5372,25 +5400,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일바이뚜</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>언니솜씨 송도점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jornardan@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1340-2987</t>
+          <t>032-832-4177</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로168번길 101 송도랜드마크푸르지오시티 상가 2층 221</t>
+          <t>인천광역시 연수구 아트센터대로97번길 30 근린상가 106호 언니솜씨</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_ddu</t>
+          <t>https://www.instagram.com/sister__nail__</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5425,13 +5457,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="Q54" t="n">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="R54" t="n">
-        <v>269</v>
+        <v>396</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5440,17 +5472,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1515520159</t>
+          <t>1559564560</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1515520159</t>
+          <t>https://m.place.naver.com/place/1559564560</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5462,29 +5494,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>여우손톱</t>
+          <t>문제성발관리센터 메디푸스 내성발톱 무좀 각질 문제성발톱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ckdwnrewq@naver.com</t>
+          <t>medifuss@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1321-6532</t>
+          <t>0507-1321-3367</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로125번길 13 아크리아1</t>
+          <t>인천광역시 연수구 아트센터대로 131 201동 213호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ckdwnrewq</t>
+          <t>https://blog.naver.com/medifuss</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5519,13 +5551,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>574</v>
+        <v>264</v>
       </c>
       <c r="Q55" t="n">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="R55" t="n">
-        <v>775</v>
+        <v>430</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5534,17 +5566,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>21216458</t>
+          <t>1696402748</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21216458</t>
+          <t>https://m.place.naver.com/place/1696402748</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5556,25 +5588,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>모모네일 인천송도점</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>네일이끌림</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>luxury24@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1449-3429</t>
+          <t>0507-1464-4142</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로274번길 55 상가동 1층 6호</t>
+          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티오피스텔상가204동2층220호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__momo.nail</t>
+          <t>https://www.instagram.com/nail_2ggellim</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5609,13 +5645,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>168</v>
+        <v>583</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="R56" t="n">
-        <v>169</v>
+        <v>682</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5624,17 +5660,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1312635729</t>
+          <t>1369252408</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312635729</t>
+          <t>https://m.place.naver.com/place/1369252408</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5646,29 +5682,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일 109 송도점</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>nail_109@naver.com</t>
-        </is>
-      </c>
+          <t>몰튼네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1319-1218</t>
+          <t>0507-1413-7890</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 131 여름동 149호</t>
+          <t>인천광역시 연수구 센트럴로 160 판매시설동 1층 148호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_109</t>
+          <t>https://www.instagram.com/molten_nailmood?igsh=MW9ob3V5dnYzM3F1aQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5683,7 +5715,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5694,7 +5726,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5703,13 +5735,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="Q57" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="R57" t="n">
-        <v>482</v>
+        <v>381</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5718,17 +5750,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1414664528</t>
+          <t>36307393</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1414664528</t>
+          <t>https://m.place.naver.com/place/36307393</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5740,25 +5772,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>포디랩 피오레네일 송도점 내성발톱 발톱무좀 발각질</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>네일뮬</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>catrabbit18@naver.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1317-7310</t>
+          <t>0507-1474-2412</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 122 송도프라자 209호</t>
+          <t>인천광역시 연수구 인천타워대로 257 B동 203호 네일뮬</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/podlab_songdo/</t>
+          <t>https://www.instagram.com/muulle?igsh=MWF0aW1tMndwa25mNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5793,13 +5829,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>652</v>
+        <v>242</v>
       </c>
       <c r="Q58" t="n">
-        <v>392</v>
+        <v>63</v>
       </c>
       <c r="R58" t="n">
-        <v>1044</v>
+        <v>305</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5808,17 +5844,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1701093046</t>
+          <t>1415557011</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701093046</t>
+          <t>https://m.place.naver.com/place/1415557011</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5830,29 +5866,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일라벨르 송도타임스페이스</t>
+          <t>송도네일무아</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>join9360@naver.com</t>
+          <t>babbab123-@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1362-9360</t>
+          <t>0507-1305-5796</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 314호 네일라벨르</t>
+          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드,G동 상가 1층 43호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/join9360</t>
+          <t>https://www.instagram.com/nail_mua_songdo?igsh=MWt6d3U1bjk1NzQweg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5867,7 +5903,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5878,7 +5914,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5887,13 +5923,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1288</v>
+        <v>153</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R59" t="n">
-        <v>1302</v>
+        <v>163</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5902,17 +5938,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1280755213</t>
+          <t>2036597442</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280755213</t>
+          <t>https://m.place.naver.com/place/2036597442</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5924,25 +5960,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일포유</t>
+          <t>러브윤네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1374-7708</t>
+          <t>032-815-3399</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 122 107호 네일포유</t>
+          <t>인천광역시 연수구 송도국제대로 261 더샵 센트럴시티 217동 상가 1층 118호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailforyou_/</t>
+          <t>https://www.instagram.com/luvyun_nail?igsh=MTB5dnRza3I1czVydA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5977,13 +6013,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="R60" t="n">
-        <v>56</v>
+        <v>231</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5992,17 +6028,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>36177492</t>
+          <t>1231000131</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36177492</t>
+          <t>https://m.place.naver.com/place/1231000131</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6014,21 +6050,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일민</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>네일모아나</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>moana48@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1403-1161</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 116 푸르지오월드마크7단지 1층 125호</t>
+          <t>인천광역시 연수구 센트럴로 232 GATE , E1 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/Nail_Minae</t>
+          <t>https://www.instagram.com/nailmoana_</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6063,13 +6107,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>301</v>
+        <v>138</v>
       </c>
       <c r="Q61" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>346</v>
+        <v>143</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6078,17 +6122,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1769913626</t>
+          <t>1865551764</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769913626</t>
+          <t>https://m.place.naver.com/place/1865551764</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6100,25 +6144,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>모찌네일</t>
+          <t>지금할일은네일로 송도점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>denise1003@naver.com</t>
+          <t>sym_ja@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1322-1498</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 C동 4층 410호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 1층 193호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mochinail_eb</t>
+          <t>https://www.instagram.com/hong_nailshop</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6153,13 +6201,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="R62" t="n">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6168,17 +6216,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1205962180</t>
+          <t>1834821209</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205962180</t>
+          <t>https://m.place.naver.com/place/1834821209</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6190,34 +6238,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>하이피네일</t>
+          <t>데이지네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>hy_p_nail@naver.com</t>
+          <t>a1070bbb@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1365-6641</t>
+          <t>0507-1444-9334</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로 70 송도AT센터 오피스텔동 107호</t>
+          <t>인천광역시 연수구 하모니로 144 A동 2층 213호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hy_p_nail</t>
+          <t>https://open.kakao.com/o/sKSaW3Sg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6238,7 +6286,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6247,13 +6295,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6262,17 +6310,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1213017361</t>
+          <t>1462227411</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213017361</t>
+          <t>https://m.place.naver.com/place/1462227411</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6284,26 +6332,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>송도네일에디크 센트럴점</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>네일포유</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nail_for_u@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1374-7708</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 185 센트럴비즈한라 2층 213일부호</t>
+          <t>인천광역시 연수구 신송로 122 107호 네일포유</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_psxeCn</t>
+          <t>https://www.instagram.com/nailforyou_/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6324,7 +6380,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6333,13 +6389,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R64" t="n">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6348,17 +6404,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1035124007</t>
+          <t>36177492</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035124007</t>
+          <t>https://m.place.naver.com/place/36177492</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6370,29 +6426,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>문제성발관리센터 메디푸스 내성발톱 무좀 각질 문제성발톱</t>
+          <t>그린닷네일 뷰티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>medifuss@naver.com</t>
+          <t>palette_j_1107@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1321-3367</t>
+          <t>0507-1351-8538</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 131 201동 213호</t>
+          <t>인천광역시 연수구 하모니로 158 C동 302호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/medifuss</t>
+          <t>https://www.instagram.com/grin.dot_nail/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6407,7 +6463,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6427,13 +6483,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>264</v>
+        <v>179</v>
       </c>
       <c r="Q65" t="n">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="R65" t="n">
-        <v>429</v>
+        <v>195</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6442,17 +6498,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1696402748</t>
+          <t>1912589928</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696402748</t>
+          <t>https://m.place.naver.com/place/1912589928</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6464,29 +6520,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>다됨네일</t>
+          <t>네일에르</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>a7814341@naver.com</t>
+          <t>zaqwsx9372@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>032-815-9344</t>
+          <t>0507-1412-8155</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도문화로28번길 27 호반베르디움 2차 아파트상가 2동 204호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 2층 211호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/a7814341</t>
+          <t>https://www.instagram.com/nail___aile/?next=undefined&amp;hl=ko</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6501,7 +6557,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6521,13 +6577,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="Q66" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R66" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6536,17 +6592,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1320993039</t>
+          <t>2024964834</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320993039</t>
+          <t>https://m.place.naver.com/place/2024964834</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6558,34 +6614,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>반디인하우스 송도점</t>
+          <t>하꼼네일 파고드는발톱 문제성발톱 발각질</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bandinhouse_songdo@naver.com</t>
+          <t>eunbyeol11@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1434-8241</t>
+          <t>0507-1364-7451</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
+          <t>인천광역시 연수구 송도과학로27번길 55 A동 2층 208호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bandinhouse_songdo</t>
+          <t>http://pf.kakao.com/_wvvmG</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6595,7 +6651,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6618,10 +6674,10 @@
         <v>270</v>
       </c>
       <c r="Q67" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>342</v>
+        <v>275</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6630,17 +6686,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1592116315</t>
+          <t>1024262947</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1592116315</t>
+          <t>https://m.place.naver.com/place/1024262947</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6652,25 +6708,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일도맑음</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>네일르블랑</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>6540067@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1370-8213</t>
+          <t>0507-1306-8906</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 1층 166호 리치센트럴</t>
+          <t>인천광역시 연수구 인천타워대로 393 305동 1층 A동 112호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_malkum</t>
+          <t>https://www.instagram.com/nail_le_blanc</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6705,13 +6765,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>441</v>
+        <v>25</v>
       </c>
       <c r="Q68" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>463</v>
+        <v>26</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6720,17 +6780,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1724575080</t>
+          <t>2085102425</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1724575080</t>
+          <t>https://m.place.naver.com/place/2085102425</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6742,30 +6802,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>뤼미에트네일</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>반디인하우스 송도점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bandinhouse_songdo@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1347-2495</t>
+          <t>0507-1434-8241</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 연구단지로55번길 16 2층 210호</t>
+          <t>인천광역시 연수구 신송로 153 더마란츠타워 114호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhgxgxon</t>
+          <t>https://blog.naver.com/bandinhouse_songdo</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6775,7 +6839,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6795,13 +6859,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>52</v>
+        <v>270</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="R69" t="n">
-        <v>52</v>
+        <v>342</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6810,17 +6874,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2019651969</t>
+          <t>1592116315</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019651969</t>
+          <t>https://m.place.naver.com/place/1592116315</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6832,30 +6896,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일퀸 송도점</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>아티카네일 송도</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>atticanail@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1364-8343</t>
+          <t>0507-1355-9531</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 165 2층</t>
+          <t>인천광역시 연수구 센트럴로 313 한라씨워크 C동 2층 258호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_PgXfn</t>
+          <t>https://blog.naver.com/atticanail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6865,7 +6933,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6885,13 +6953,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="R70" t="n">
-        <v>56</v>
+        <v>341</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6900,17 +6968,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1969782774</t>
+          <t>1192730169</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1969782774</t>
+          <t>https://m.place.naver.com/place/1192730169</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6990,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일1607</t>
+          <t>네일민</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -6931,12 +6999,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-7 송도 대경스위트리아 파크뷰, 1층 111호</t>
+          <t>인천광역시 연수구 컨벤시아대로 116 푸르지오월드마크7단지 1층 125호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail160_7</t>
+          <t>https://www.instagram.com/Nail_Minae</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6962,7 +7030,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6971,13 +7039,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>446</v>
+        <v>301</v>
       </c>
       <c r="Q71" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="R71" t="n">
-        <v>477</v>
+        <v>346</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6986,17 +7054,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1249527516</t>
+          <t>1769913626</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249527516</t>
+          <t>https://m.place.naver.com/place/1769913626</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7008,25 +7076,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>차차뷰티네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>오뉴월뷰티</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>vanilla__-@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1345-2926</t>
+          <t>0507-1338-4181</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 B동 239호</t>
+          <t>인천광역시 연수구 하모니로 158 c동 210호 오뉴월뷰티</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://instagram.com/chachabt_1</t>
+          <t>http://www.instagram.com/onewwol_bty</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7061,13 +7133,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>276</v>
+        <v>702</v>
       </c>
       <c r="Q72" t="n">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="R72" t="n">
-        <v>354</v>
+        <v>874</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7076,17 +7148,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1945183541</t>
+          <t>1572480675</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945183541</t>
+          <t>https://m.place.naver.com/place/1572480675</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7098,29 +7170,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>인어뷰티 송도점</t>
+          <t>다됨네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>in_awe_beauty@naver.com</t>
+          <t>a7814341@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1397-2403</t>
+          <t>032-815-9344</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도미래로11번길 27 B동 2층 213호 인어뷰티 송도점</t>
+          <t>인천광역시 연수구 송도문화로28번길 27 호반베르디움 2차 아파트상가 2동 204호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/in.awe.beauty</t>
+          <t>https://blog.naver.com/a7814341</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7135,7 +7207,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7155,13 +7227,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>666</v>
+        <v>128</v>
       </c>
       <c r="Q73" t="n">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="R73" t="n">
-        <v>796</v>
+        <v>144</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7170,17 +7242,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1323913451</t>
+          <t>1320993039</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323913451</t>
+          <t>https://m.place.naver.com/place/1320993039</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7192,34 +7264,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>비지트네일</t>
+          <t>누오네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>visitnail@naver.com</t>
+          <t>chlwodbsl@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1394-9422</t>
+          <t>0507-1481-2504</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 C동 341호</t>
+          <t>인천광역시 연수구 신송로 165-17 2층 231호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/visitnail</t>
+          <t>http://pf.kakao.com/_rJBWG</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7229,7 +7301,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7240,7 +7312,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7249,13 +7321,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="Q74" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="R74" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7264,17 +7336,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1503164148</t>
+          <t>1196589400</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503164148</t>
+          <t>https://m.place.naver.com/place/1196589400</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7286,29 +7358,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>볼네일 인천송도점</t>
+          <t>힐링네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ballnail-@naver.com</t>
+          <t>lovekeiti@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1341-0638</t>
+          <t>0507-1330-2935</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 A동 1층 129-1호</t>
+          <t>인천광역시 연수구 해돋이로 107 G동 1층 상가56호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ballnail_</t>
+          <t>https://www.instagram.com/healing08_nail/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7343,13 +7415,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>391</v>
+        <v>59</v>
       </c>
       <c r="Q75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R75" t="n">
-        <v>406</v>
+        <v>69</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7358,17 +7430,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2002201349</t>
+          <t>35051773</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002201349</t>
+          <t>https://m.place.naver.com/place/35051773</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7380,25 +7452,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>앤드네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>네일라벨르 송도타임스페이스</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>join9360@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1478-8939</t>
+          <t>0507-1362-9360</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 판매시설 2층 230호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 314호 네일라벨르</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_andnail</t>
+          <t>https://blog.naver.com/join9360</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7413,7 +7489,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7424,7 +7500,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7433,13 +7509,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>328</v>
+        <v>1288</v>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R76" t="n">
-        <v>333</v>
+        <v>1302</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7448,17 +7524,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1327958684</t>
+          <t>1280755213</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327958684</t>
+          <t>https://m.place.naver.com/place/1280755213</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
